--- a/projects/mobile-price-tracker/backups/mobile_plans_2026-06-22.xlsx
+++ b/projects/mobile-price-tracker/backups/mobile_plans_2026-06-22.xlsx
@@ -12,14 +12,14 @@
     <sheet name="changes" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="summary" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="comparison" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Vivo" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Claro" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="TIM" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Ranking" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Vivo" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Claro" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="TIM" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'history'!$A$1:$T$52</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'latest'!$A$1:$T$52</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'changes'!$A$1:$I$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -58,11 +58,6 @@
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Arial"/>
       <i val="1"/>
       <color rgb="00808080"/>
       <sz val="9"/>
@@ -70,10 +65,15 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <color rgb="001F3864"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -85,8 +85,23 @@
         <fgColor rgb="001F3864"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F5FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6E0F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -94,28 +109,73 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00FFFFFF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <b val="1"/>
+        <color rgb="00006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -186,6 +246,887 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Control — cheapest R$ over time</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'comparison'!B36</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="20000">
+              <a:solidFill>
+                <a:srgbClr val="0033A0"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="6"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'comparison'!$A$37</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'comparison'!$B$37</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'comparison'!C36</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="20000">
+              <a:solidFill>
+                <a:srgbClr val="660099"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="6"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'comparison'!$A$37</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'comparison'!$C$37</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'comparison'!D36</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="20000">
+              <a:solidFill>
+                <a:srgbClr val="DA291C"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="6"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'comparison'!$A$37</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'comparison'!$D$37</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Date</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>R$</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Post — cheapest R$ over time</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'comparison'!E36</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="20000">
+              <a:solidFill>
+                <a:srgbClr val="0033A0"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="6"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'comparison'!$A$37</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'comparison'!$E$37</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'comparison'!F36</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="20000">
+              <a:solidFill>
+                <a:srgbClr val="660099"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="6"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'comparison'!$A$37</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'comparison'!$F$37</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'comparison'!G36</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="20000">
+              <a:solidFill>
+                <a:srgbClr val="DA291C"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="6"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'comparison'!$A$37</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'comparison'!$G$37</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Date</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>R$</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Pre — cheapest R$ over time</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'comparison'!H36</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="20000">
+              <a:solidFill>
+                <a:srgbClr val="0033A0"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="6"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'comparison'!$A$37</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'comparison'!$H$37</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'comparison'!I36</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="20000">
+              <a:solidFill>
+                <a:srgbClr val="660099"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="6"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'comparison'!$A$37</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'comparison'!$I$37</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'comparison'!J36</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="20000">
+              <a:solidFill>
+                <a:srgbClr val="DA291C"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="6"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'comparison'!$A$37</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'comparison'!$J$37</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Date</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>R$</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Digital — cheapest R$ over time</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'comparison'!K36</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="20000">
+              <a:solidFill>
+                <a:srgbClr val="0033A0"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="6"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'comparison'!$A$37</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'comparison'!$K$37</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'comparison'!L36</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="20000">
+              <a:solidFill>
+                <a:srgbClr val="660099"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="6"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'comparison'!$A$37</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'comparison'!$L$37</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'comparison'!M36</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="20000">
+              <a:solidFill>
+                <a:srgbClr val="DA291C"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="6"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'comparison'!$A$37</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'comparison'!$M$37</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Date</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>R$</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4140000" cy="2592000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4140000" cy="2592000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4140000" cy="2592000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4140000" cy="2592000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="4" name="Chart 4"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -474,6 +1415,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="008A8A8A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -612,7 +1554,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -681,70 +1623,70 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>claro</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>Controle 30GB</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>claro:plano-controle-30gb</t>
         </is>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="H3" s="6" t="n">
         <v>69.90000000000001</v>
       </c>
-      <c r="I3" s="3" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="4" t="n">
+      <c r="I3" s="6" t="inlineStr"/>
+      <c r="J3" s="5" t="inlineStr"/>
+      <c r="K3" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="L3" s="5" t="inlineStr"/>
+      <c r="M3" s="5" t="inlineStr">
         <is>
           <t>WhatsApp</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr"/>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="2" t="inlineStr">
+      <c r="N3" s="5" t="inlineStr"/>
+      <c r="O3" s="5" t="inlineStr"/>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr"/>
+      <c r="R3" s="5" t="inlineStr">
         <is>
           <t>Para uso livre; Bônus do Hexa para uso livre; Bônus para redes sociais e apps; Redes sociais e apps; WhatsApp ilimitado</t>
         </is>
       </c>
-      <c r="S3" s="2" t="inlineStr">
+      <c r="S3" s="5" t="inlineStr">
         <is>
           <t>https://www.claro.com.br/celular/controle</t>
         </is>
       </c>
-      <c r="T3" s="2" t="inlineStr">
+      <c r="T3" s="5" t="inlineStr">
         <is>
           <t>data/raw/claro_control_SP.json</t>
         </is>
@@ -758,7 +1700,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -821,70 +1763,70 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>claro</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>flex</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Flex 15GB</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>claro:plano-flex-15gb</t>
         </is>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="H5" s="6" t="n">
         <v>44.9</v>
       </c>
-      <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="4" t="n">
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="5" t="inlineStr"/>
+      <c r="K5" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="L5" s="5" t="inlineStr"/>
+      <c r="M5" s="5" t="inlineStr">
         <is>
           <t>WhatsApp</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr"/>
-      <c r="O5" s="2" t="inlineStr"/>
-      <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr"/>
-      <c r="R5" s="2" t="inlineStr">
+      <c r="N5" s="5" t="inlineStr"/>
+      <c r="O5" s="5" t="inlineStr"/>
+      <c r="P5" s="5" t="inlineStr"/>
+      <c r="Q5" s="5" t="inlineStr"/>
+      <c r="R5" s="5" t="inlineStr">
         <is>
           <t>Para uso livre; Bônus do Hexa para uso livre; Para redes sociais e apps; Bônus extra nos apps; WhatsApp ilimitado</t>
         </is>
       </c>
-      <c r="S5" s="2" t="inlineStr">
+      <c r="S5" s="5" t="inlineStr">
         <is>
           <t>https://www.claro.com.br/celular/flex</t>
         </is>
       </c>
-      <c r="T5" s="2" t="inlineStr">
+      <c r="T5" s="5" t="inlineStr">
         <is>
           <t>data/raw/claro_flex_SP.json</t>
         </is>
@@ -898,7 +1840,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -961,70 +1903,70 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>claro</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>flex</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>Flex 30GB</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>claro:plano-flex-30gb</t>
         </is>
       </c>
-      <c r="H7" s="3" t="n">
+      <c r="H7" s="6" t="n">
         <v>69.90000000000001</v>
       </c>
-      <c r="I7" s="3" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="4" t="n">
+      <c r="I7" s="6" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr"/>
+      <c r="K7" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="L7" s="5" t="inlineStr"/>
+      <c r="M7" s="5" t="inlineStr">
         <is>
           <t>WhatsApp</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr"/>
-      <c r="O7" s="2" t="inlineStr"/>
-      <c r="P7" s="2" t="inlineStr"/>
-      <c r="Q7" s="2" t="inlineStr"/>
-      <c r="R7" s="2" t="inlineStr">
+      <c r="N7" s="5" t="inlineStr"/>
+      <c r="O7" s="5" t="inlineStr"/>
+      <c r="P7" s="5" t="inlineStr"/>
+      <c r="Q7" s="5" t="inlineStr"/>
+      <c r="R7" s="5" t="inlineStr">
         <is>
           <t>Para uso livre; Bônus do Hexa para uso livre; Para redes sociais e apps; Bônus extra nos apps; WhatsApp ilimitado; Assinatura Claro musica inclusa</t>
         </is>
       </c>
-      <c r="S7" s="2" t="inlineStr">
+      <c r="S7" s="5" t="inlineStr">
         <is>
           <t>https://www.claro.com.br/celular/flex</t>
         </is>
       </c>
-      <c r="T7" s="2" t="inlineStr">
+      <c r="T7" s="5" t="inlineStr">
         <is>
           <t>data/raw/claro_flex_SP.json</t>
         </is>
@@ -1038,7 +1980,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1101,70 +2043,70 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>claro</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>postpaid</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>Pós 100GB</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>claro:plano-pos-100gb</t>
         </is>
       </c>
-      <c r="H9" s="3" t="n">
+      <c r="H9" s="6" t="n">
         <v>179.9</v>
       </c>
-      <c r="I9" s="3" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="4" t="n">
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr"/>
+      <c r="K9" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="L9" s="5" t="inlineStr"/>
+      <c r="M9" s="5" t="inlineStr">
         <is>
           <t>WhatsApp</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr"/>
-      <c r="O9" s="2" t="inlineStr"/>
-      <c r="P9" s="2" t="inlineStr"/>
-      <c r="Q9" s="2" t="inlineStr"/>
-      <c r="R9" s="2" t="inlineStr">
+      <c r="N9" s="5" t="inlineStr"/>
+      <c r="O9" s="5" t="inlineStr"/>
+      <c r="P9" s="5" t="inlineStr"/>
+      <c r="Q9" s="5" t="inlineStr"/>
+      <c r="R9" s="5" t="inlineStr">
         <is>
           <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Américas; Claro Sync: Smartwatch conectado</t>
         </is>
       </c>
-      <c r="S9" s="2" t="inlineStr">
+      <c r="S9" s="5" t="inlineStr">
         <is>
           <t>https://www.claro.com.br/celular/pos</t>
         </is>
       </c>
-      <c r="T9" s="2" t="inlineStr">
+      <c r="T9" s="5" t="inlineStr">
         <is>
           <t>data/raw/claro_postpaid_SP.json</t>
         </is>
@@ -1178,7 +2120,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1241,70 +2183,70 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>claro</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>postpaid</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>Pós 200GB</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>claro:plano-pos-200gb</t>
         </is>
       </c>
-      <c r="H11" s="3" t="n">
+      <c r="H11" s="6" t="n">
         <v>339.9</v>
       </c>
-      <c r="I11" s="3" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="4" t="n">
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="5" t="inlineStr"/>
+      <c r="K11" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="L11" s="5" t="inlineStr"/>
+      <c r="M11" s="5" t="inlineStr">
         <is>
           <t>WhatsApp</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr"/>
-      <c r="O11" s="2" t="inlineStr"/>
-      <c r="P11" s="2" t="inlineStr"/>
-      <c r="Q11" s="2" t="inlineStr"/>
-      <c r="R11" s="2" t="inlineStr">
+      <c r="N11" s="5" t="inlineStr"/>
+      <c r="O11" s="5" t="inlineStr"/>
+      <c r="P11" s="5" t="inlineStr"/>
+      <c r="Q11" s="5" t="inlineStr"/>
+      <c r="R11" s="5" t="inlineStr">
         <is>
           <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Mundo; Claro Sync: Smartwatch conectado</t>
         </is>
       </c>
-      <c r="S11" s="2" t="inlineStr">
+      <c r="S11" s="5" t="inlineStr">
         <is>
           <t>https://www.claro.com.br/celular/pos</t>
         </is>
       </c>
-      <c r="T11" s="2" t="inlineStr">
+      <c r="T11" s="5" t="inlineStr">
         <is>
           <t>data/raw/claro_postpaid_SP.json</t>
         </is>
@@ -1318,7 +2260,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1381,70 +2323,70 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>claro</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>postpaid</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>Pós 60GB</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>claro:plano-pos-60gb</t>
         </is>
       </c>
-      <c r="H13" s="3" t="n">
+      <c r="H13" s="6" t="n">
         <v>124.9</v>
       </c>
-      <c r="I13" s="3" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="4" t="n">
+      <c r="I13" s="6" t="inlineStr"/>
+      <c r="J13" s="5" t="inlineStr"/>
+      <c r="K13" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="L13" s="5" t="inlineStr"/>
+      <c r="M13" s="5" t="inlineStr">
         <is>
           <t>WhatsApp</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr"/>
-      <c r="O13" s="2" t="inlineStr"/>
-      <c r="P13" s="2" t="inlineStr"/>
-      <c r="Q13" s="2" t="inlineStr"/>
-      <c r="R13" s="2" t="inlineStr">
+      <c r="N13" s="5" t="inlineStr"/>
+      <c r="O13" s="5" t="inlineStr"/>
+      <c r="P13" s="5" t="inlineStr"/>
+      <c r="Q13" s="5" t="inlineStr"/>
+      <c r="R13" s="5" t="inlineStr">
         <is>
           <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Américas; Claro Sync: Smartwatch conectado</t>
         </is>
       </c>
-      <c r="S13" s="2" t="inlineStr">
+      <c r="S13" s="5" t="inlineStr">
         <is>
           <t>https://www.claro.com.br/celular/pos</t>
         </is>
       </c>
-      <c r="T13" s="2" t="inlineStr">
+      <c r="T13" s="5" t="inlineStr">
         <is>
           <t>data/raw/claro_postpaid_SP.json</t>
         </is>
@@ -1458,7 +2400,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1517,62 +2459,62 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>tim</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>TIM Controle 41GB</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>tim:162901</t>
         </is>
       </c>
-      <c r="H15" s="3" t="n">
+      <c r="H15" s="6" t="n">
         <v>58.99</v>
       </c>
-      <c r="I15" s="3" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="4" t="n">
+      <c r="I15" s="6" t="inlineStr"/>
+      <c r="J15" s="5" t="inlineStr"/>
+      <c r="K15" s="7" t="n">
         <v>41</v>
       </c>
-      <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="2" t="inlineStr"/>
-      <c r="N15" s="2" t="inlineStr"/>
-      <c r="O15" s="2" t="inlineStr"/>
-      <c r="P15" s="2" t="inlineStr"/>
-      <c r="Q15" s="2" t="inlineStr"/>
-      <c r="R15" s="2" t="inlineStr"/>
-      <c r="S15" s="2" t="inlineStr">
+      <c r="L15" s="5" t="inlineStr"/>
+      <c r="M15" s="5" t="inlineStr"/>
+      <c r="N15" s="5" t="inlineStr"/>
+      <c r="O15" s="5" t="inlineStr"/>
+      <c r="P15" s="5" t="inlineStr"/>
+      <c r="Q15" s="5" t="inlineStr"/>
+      <c r="R15" s="5" t="inlineStr"/>
+      <c r="S15" s="5" t="inlineStr">
         <is>
           <t>https://www.tim.com.br/sp/para-voce/planos/controle</t>
         </is>
       </c>
-      <c r="T15" s="2" t="inlineStr">
+      <c r="T15" s="5" t="inlineStr">
         <is>
           <t>data/raw/tim_control_SP.html</t>
         </is>
@@ -1586,7 +2528,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1641,62 +2583,62 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>tim</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>TIM Controle Plus 45GB</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>tim:155891</t>
         </is>
       </c>
-      <c r="H17" s="3" t="n">
+      <c r="H17" s="6" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="I17" s="3" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="4" t="n">
+      <c r="I17" s="6" t="inlineStr"/>
+      <c r="J17" s="5" t="inlineStr"/>
+      <c r="K17" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="2" t="inlineStr"/>
-      <c r="N17" s="2" t="inlineStr"/>
-      <c r="O17" s="2" t="inlineStr"/>
-      <c r="P17" s="2" t="inlineStr"/>
-      <c r="Q17" s="2" t="inlineStr"/>
-      <c r="R17" s="2" t="inlineStr"/>
-      <c r="S17" s="2" t="inlineStr">
+      <c r="L17" s="5" t="inlineStr"/>
+      <c r="M17" s="5" t="inlineStr"/>
+      <c r="N17" s="5" t="inlineStr"/>
+      <c r="O17" s="5" t="inlineStr"/>
+      <c r="P17" s="5" t="inlineStr"/>
+      <c r="Q17" s="5" t="inlineStr"/>
+      <c r="R17" s="5" t="inlineStr"/>
+      <c r="S17" s="5" t="inlineStr">
         <is>
           <t>https://www.tim.com.br/sp/para-voce/planos/controle</t>
         </is>
       </c>
-      <c r="T17" s="2" t="inlineStr">
+      <c r="T17" s="5" t="inlineStr">
         <is>
           <t>data/raw/tim_control_SP.html</t>
         </is>
@@ -1710,7 +2652,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1765,60 +2707,60 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>tim</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>TIM Controle Pro Express</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>tim:143576</t>
         </is>
       </c>
-      <c r="H19" s="3" t="n">
+      <c r="H19" s="6" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="I19" s="3" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr"/>
-      <c r="K19" s="4" t="inlineStr"/>
-      <c r="L19" s="2" t="inlineStr"/>
-      <c r="M19" s="2" t="inlineStr"/>
-      <c r="N19" s="2" t="inlineStr"/>
-      <c r="O19" s="2" t="inlineStr"/>
-      <c r="P19" s="2" t="inlineStr"/>
-      <c r="Q19" s="2" t="inlineStr"/>
-      <c r="R19" s="2" t="inlineStr"/>
-      <c r="S19" s="2" t="inlineStr">
+      <c r="I19" s="6" t="inlineStr"/>
+      <c r="J19" s="5" t="inlineStr"/>
+      <c r="K19" s="7" t="inlineStr"/>
+      <c r="L19" s="5" t="inlineStr"/>
+      <c r="M19" s="5" t="inlineStr"/>
+      <c r="N19" s="5" t="inlineStr"/>
+      <c r="O19" s="5" t="inlineStr"/>
+      <c r="P19" s="5" t="inlineStr"/>
+      <c r="Q19" s="5" t="inlineStr"/>
+      <c r="R19" s="5" t="inlineStr"/>
+      <c r="S19" s="5" t="inlineStr">
         <is>
           <t>https://www.tim.com.br/sp/para-voce/planos/controle</t>
         </is>
       </c>
-      <c r="T19" s="2" t="inlineStr">
+      <c r="T19" s="5" t="inlineStr">
         <is>
           <t>data/raw/tim_control_SP.html</t>
         </is>
@@ -1832,7 +2774,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1887,62 +2829,62 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>tim</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>postpaid</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>TIM Black A Express 67GB</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>tim:55121</t>
         </is>
       </c>
-      <c r="H21" s="3" t="n">
+      <c r="H21" s="6" t="n">
         <v>119.99</v>
       </c>
-      <c r="I21" s="3" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr"/>
-      <c r="K21" s="4" t="n">
+      <c r="I21" s="6" t="inlineStr"/>
+      <c r="J21" s="5" t="inlineStr"/>
+      <c r="K21" s="7" t="n">
         <v>67</v>
       </c>
-      <c r="L21" s="2" t="inlineStr"/>
-      <c r="M21" s="2" t="inlineStr"/>
-      <c r="N21" s="2" t="inlineStr"/>
-      <c r="O21" s="2" t="inlineStr"/>
-      <c r="P21" s="2" t="inlineStr"/>
-      <c r="Q21" s="2" t="inlineStr"/>
-      <c r="R21" s="2" t="inlineStr"/>
-      <c r="S21" s="2" t="inlineStr">
+      <c r="L21" s="5" t="inlineStr"/>
+      <c r="M21" s="5" t="inlineStr"/>
+      <c r="N21" s="5" t="inlineStr"/>
+      <c r="O21" s="5" t="inlineStr"/>
+      <c r="P21" s="5" t="inlineStr"/>
+      <c r="Q21" s="5" t="inlineStr"/>
+      <c r="R21" s="5" t="inlineStr"/>
+      <c r="S21" s="5" t="inlineStr">
         <is>
           <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
         </is>
       </c>
-      <c r="T21" s="2" t="inlineStr">
+      <c r="T21" s="5" t="inlineStr">
         <is>
           <t>data/raw/tim_postpaid_SP.html</t>
         </is>
@@ -1956,7 +2898,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2011,62 +2953,62 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>tim</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>postpaid</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>TIM Black C Express 107GB</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>tim:52151</t>
         </is>
       </c>
-      <c r="H23" s="3" t="n">
+      <c r="H23" s="6" t="n">
         <v>164.99</v>
       </c>
-      <c r="I23" s="3" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr"/>
-      <c r="K23" s="4" t="n">
+      <c r="I23" s="6" t="inlineStr"/>
+      <c r="J23" s="5" t="inlineStr"/>
+      <c r="K23" s="7" t="n">
         <v>107</v>
       </c>
-      <c r="L23" s="2" t="inlineStr"/>
-      <c r="M23" s="2" t="inlineStr"/>
-      <c r="N23" s="2" t="inlineStr"/>
-      <c r="O23" s="2" t="inlineStr"/>
-      <c r="P23" s="2" t="inlineStr"/>
-      <c r="Q23" s="2" t="inlineStr"/>
-      <c r="R23" s="2" t="inlineStr"/>
-      <c r="S23" s="2" t="inlineStr">
+      <c r="L23" s="5" t="inlineStr"/>
+      <c r="M23" s="5" t="inlineStr"/>
+      <c r="N23" s="5" t="inlineStr"/>
+      <c r="O23" s="5" t="inlineStr"/>
+      <c r="P23" s="5" t="inlineStr"/>
+      <c r="Q23" s="5" t="inlineStr"/>
+      <c r="R23" s="5" t="inlineStr"/>
+      <c r="S23" s="5" t="inlineStr">
         <is>
           <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
         </is>
       </c>
-      <c r="T23" s="2" t="inlineStr">
+      <c r="T23" s="5" t="inlineStr">
         <is>
           <t>data/raw/tim_postpaid_SP.html</t>
         </is>
@@ -2080,7 +3022,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2135,62 +3077,62 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>tim</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>postpaid</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>TIM Black Plus 80GB</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>tim:54256</t>
         </is>
       </c>
-      <c r="H25" s="3" t="n">
+      <c r="H25" s="6" t="n">
         <v>149.99</v>
       </c>
-      <c r="I25" s="3" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr"/>
-      <c r="K25" s="4" t="n">
+      <c r="I25" s="6" t="inlineStr"/>
+      <c r="J25" s="5" t="inlineStr"/>
+      <c r="K25" s="7" t="n">
         <v>80</v>
       </c>
-      <c r="L25" s="2" t="inlineStr"/>
-      <c r="M25" s="2" t="inlineStr"/>
-      <c r="N25" s="2" t="inlineStr"/>
-      <c r="O25" s="2" t="inlineStr"/>
-      <c r="P25" s="2" t="inlineStr"/>
-      <c r="Q25" s="2" t="inlineStr"/>
-      <c r="R25" s="2" t="inlineStr"/>
-      <c r="S25" s="2" t="inlineStr">
+      <c r="L25" s="5" t="inlineStr"/>
+      <c r="M25" s="5" t="inlineStr"/>
+      <c r="N25" s="5" t="inlineStr"/>
+      <c r="O25" s="5" t="inlineStr"/>
+      <c r="P25" s="5" t="inlineStr"/>
+      <c r="Q25" s="5" t="inlineStr"/>
+      <c r="R25" s="5" t="inlineStr"/>
+      <c r="S25" s="5" t="inlineStr">
         <is>
           <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
         </is>
       </c>
-      <c r="T25" s="2" t="inlineStr">
+      <c r="T25" s="5" t="inlineStr">
         <is>
           <t>data/raw/tim_postpaid_SP.html</t>
         </is>
@@ -2204,7 +3146,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2259,62 +3201,62 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>tim</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>prepaid</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>TIM Pré XIP Plus 16GB</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>tim:106306</t>
         </is>
       </c>
-      <c r="H27" s="3" t="n">
+      <c r="H27" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="I27" s="3" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr"/>
-      <c r="K27" s="4" t="n">
+      <c r="I27" s="6" t="inlineStr"/>
+      <c r="J27" s="5" t="inlineStr"/>
+      <c r="K27" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="L27" s="2" t="inlineStr"/>
-      <c r="M27" s="2" t="inlineStr"/>
-      <c r="N27" s="2" t="inlineStr"/>
-      <c r="O27" s="2" t="inlineStr"/>
-      <c r="P27" s="2" t="inlineStr"/>
-      <c r="Q27" s="2" t="inlineStr"/>
-      <c r="R27" s="2" t="inlineStr"/>
-      <c r="S27" s="2" t="inlineStr">
+      <c r="L27" s="5" t="inlineStr"/>
+      <c r="M27" s="5" t="inlineStr"/>
+      <c r="N27" s="5" t="inlineStr"/>
+      <c r="O27" s="5" t="inlineStr"/>
+      <c r="P27" s="5" t="inlineStr"/>
+      <c r="Q27" s="5" t="inlineStr"/>
+      <c r="R27" s="5" t="inlineStr"/>
+      <c r="S27" s="5" t="inlineStr">
         <is>
           <t>https://www.tim.com.br/sp/para-voce/planos/pre-pago</t>
         </is>
       </c>
-      <c r="T27" s="2" t="inlineStr">
+      <c r="T27" s="5" t="inlineStr">
         <is>
           <t>data/raw/tim_prepaid_SP.html</t>
         </is>
@@ -2328,7 +3270,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2383,62 +3325,62 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>tim</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>prepaid</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>TIM Pré XIP Plus 8GB</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>tim:59901</t>
         </is>
       </c>
-      <c r="H29" s="3" t="n">
+      <c r="H29" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="I29" s="3" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr"/>
-      <c r="K29" s="4" t="n">
+      <c r="I29" s="6" t="inlineStr"/>
+      <c r="J29" s="5" t="inlineStr"/>
+      <c r="K29" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="L29" s="2" t="inlineStr"/>
-      <c r="M29" s="2" t="inlineStr"/>
-      <c r="N29" s="2" t="inlineStr"/>
-      <c r="O29" s="2" t="inlineStr"/>
-      <c r="P29" s="2" t="inlineStr"/>
-      <c r="Q29" s="2" t="inlineStr"/>
-      <c r="R29" s="2" t="inlineStr"/>
-      <c r="S29" s="2" t="inlineStr">
+      <c r="L29" s="5" t="inlineStr"/>
+      <c r="M29" s="5" t="inlineStr"/>
+      <c r="N29" s="5" t="inlineStr"/>
+      <c r="O29" s="5" t="inlineStr"/>
+      <c r="P29" s="5" t="inlineStr"/>
+      <c r="Q29" s="5" t="inlineStr"/>
+      <c r="R29" s="5" t="inlineStr"/>
+      <c r="S29" s="5" t="inlineStr">
         <is>
           <t>https://www.tim.com.br/sp/para-voce/planos/pre-pago</t>
         </is>
       </c>
-      <c r="T29" s="2" t="inlineStr">
+      <c r="T29" s="5" t="inlineStr">
         <is>
           <t>data/raw/tim_prepaid_SP.html</t>
         </is>
@@ -2452,7 +3394,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2515,70 +3457,70 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>vivo</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>Vivo Controle</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>vivo:VIV202600029300-51gb</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="I31" s="3" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr"/>
-      <c r="K31" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029300-61gb</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="I31" s="6" t="inlineStr"/>
+      <c r="J31" s="5" t="inlineStr"/>
+      <c r="K31" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
         <is>
           <t>20 GB de franquia 31 GB de bônus</t>
         </is>
       </c>
-      <c r="M31" s="2" t="inlineStr"/>
-      <c r="N31" s="2" t="inlineStr"/>
-      <c r="O31" s="2" t="inlineStr"/>
-      <c r="P31" s="2" t="inlineStr"/>
-      <c r="Q31" s="2" t="inlineStr"/>
-      <c r="R31" s="2" t="inlineStr">
+      <c r="M31" s="5" t="inlineStr"/>
+      <c r="N31" s="5" t="inlineStr"/>
+      <c r="O31" s="5" t="inlineStr"/>
+      <c r="P31" s="5" t="inlineStr"/>
+      <c r="Q31" s="5" t="inlineStr"/>
+      <c r="R31" s="5" t="inlineStr">
         <is>
           <t>6 meses grátis de Gemini com AI Plus</t>
         </is>
       </c>
-      <c r="S31" s="2" t="inlineStr">
+      <c r="S31" s="5" t="inlineStr">
         <is>
           <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
         </is>
       </c>
-      <c r="T31" s="2" t="inlineStr">
+      <c r="T31" s="5" t="inlineStr">
         <is>
           <t>data/raw/vivo_control_SP.html</t>
         </is>
@@ -2592,7 +3534,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2617,16 +3559,16 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029273-51gb</t>
+          <t>vivo:VIV202600029273-61gb</t>
         </is>
       </c>
       <c r="H32" s="3" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="I32" s="3" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="4" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
@@ -2655,70 +3597,70 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>vivo</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>Vivo Controle Entretenimento</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>vivo:VIV202600029307-51gb</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="n">
-        <v>105</v>
-      </c>
-      <c r="I33" s="3" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr"/>
-      <c r="K33" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029307-61gb</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>110</v>
+      </c>
+      <c r="I33" s="6" t="inlineStr"/>
+      <c r="J33" s="5" t="inlineStr"/>
+      <c r="K33" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
         <is>
           <t>20 GB de franquia 31 GB de bônus</t>
         </is>
       </c>
-      <c r="M33" s="2" t="inlineStr"/>
-      <c r="N33" s="2" t="inlineStr"/>
-      <c r="O33" s="2" t="inlineStr"/>
-      <c r="P33" s="2" t="inlineStr"/>
-      <c r="Q33" s="2" t="inlineStr"/>
-      <c r="R33" s="2" t="inlineStr">
+      <c r="M33" s="5" t="inlineStr"/>
+      <c r="N33" s="5" t="inlineStr"/>
+      <c r="O33" s="5" t="inlineStr"/>
+      <c r="P33" s="5" t="inlineStr"/>
+      <c r="Q33" s="5" t="inlineStr"/>
+      <c r="R33" s="5" t="inlineStr">
         <is>
           <t>Assinatura Vivo TV Inicial inclusa</t>
         </is>
       </c>
-      <c r="S33" s="2" t="inlineStr">
+      <c r="S33" s="5" t="inlineStr">
         <is>
           <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
         </is>
       </c>
-      <c r="T33" s="2" t="inlineStr">
+      <c r="T33" s="5" t="inlineStr">
         <is>
           <t>data/raw/vivo_control_SP.html</t>
         </is>
@@ -2732,7 +3674,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2757,16 +3699,16 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029313-51gb</t>
+          <t>vivo:VIV202600029313-61gb</t>
         </is>
       </c>
       <c r="H34" s="3" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I34" s="3" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="4" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
@@ -2795,70 +3737,70 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>vivo</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>Vivo Controle Netflix</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>vivo:VIV202600029308-51gb</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="I35" s="3" t="inlineStr"/>
-      <c r="J35" s="2" t="inlineStr"/>
-      <c r="K35" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029308-61gb</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="n">
+        <v>95</v>
+      </c>
+      <c r="I35" s="6" t="inlineStr"/>
+      <c r="J35" s="5" t="inlineStr"/>
+      <c r="K35" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
         <is>
           <t>20 GB de franquia 31 GB de bônus</t>
         </is>
       </c>
-      <c r="M35" s="2" t="inlineStr"/>
-      <c r="N35" s="2" t="inlineStr"/>
-      <c r="O35" s="2" t="inlineStr"/>
-      <c r="P35" s="2" t="inlineStr"/>
-      <c r="Q35" s="2" t="inlineStr"/>
-      <c r="R35" s="2" t="inlineStr">
+      <c r="M35" s="5" t="inlineStr"/>
+      <c r="N35" s="5" t="inlineStr"/>
+      <c r="O35" s="5" t="inlineStr"/>
+      <c r="P35" s="5" t="inlineStr"/>
+      <c r="Q35" s="5" t="inlineStr"/>
+      <c r="R35" s="5" t="inlineStr">
         <is>
           <t>Assinatura Netflix Padrão com anúncios</t>
         </is>
       </c>
-      <c r="S35" s="2" t="inlineStr">
+      <c r="S35" s="5" t="inlineStr">
         <is>
           <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
         </is>
       </c>
-      <c r="T35" s="2" t="inlineStr">
+      <c r="T35" s="5" t="inlineStr">
         <is>
           <t>data/raw/vivo_control_SP.html</t>
         </is>
@@ -2872,7 +3814,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2897,16 +3839,16 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029301-51gb</t>
+          <t>vivo:VIV202600029301-61gb</t>
         </is>
       </c>
       <c r="H36" s="3" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="I36" s="3" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="4" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
@@ -2935,66 +3877,66 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>vivo</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>lite</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>Easy Lite</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>vivo:VIV202600005312-30gb</t>
         </is>
       </c>
-      <c r="H37" s="3" t="n">
+      <c r="H37" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="I37" s="3" t="inlineStr"/>
-      <c r="J37" s="2" t="inlineStr"/>
-      <c r="K37" s="4" t="n">
+      <c r="I37" s="6" t="inlineStr"/>
+      <c r="J37" s="5" t="inlineStr"/>
+      <c r="K37" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="L37" s="2" t="inlineStr">
+      <c r="L37" s="5" t="inlineStr">
         <is>
           <t>30 GB de franquia 2 Meses de YouTube ilimitado</t>
         </is>
       </c>
-      <c r="M37" s="2" t="inlineStr"/>
-      <c r="N37" s="2" t="inlineStr"/>
-      <c r="O37" s="2" t="inlineStr"/>
-      <c r="P37" s="2" t="inlineStr"/>
-      <c r="Q37" s="2" t="inlineStr"/>
-      <c r="R37" s="2" t="inlineStr"/>
-      <c r="S37" s="2" t="inlineStr">
+      <c r="M37" s="5" t="inlineStr"/>
+      <c r="N37" s="5" t="inlineStr"/>
+      <c r="O37" s="5" t="inlineStr"/>
+      <c r="P37" s="5" t="inlineStr"/>
+      <c r="Q37" s="5" t="inlineStr"/>
+      <c r="R37" s="5" t="inlineStr"/>
+      <c r="S37" s="5" t="inlineStr">
         <is>
           <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/easy-lite</t>
         </is>
       </c>
-      <c r="T37" s="2" t="inlineStr">
+      <c r="T37" s="5" t="inlineStr">
         <is>
           <t>data/raw/vivo_lite_SP.html</t>
         </is>
@@ -3008,7 +3950,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3067,66 +4009,66 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>vivo</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>lite</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>Easy Lite</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>vivo:VIV202600019132-20gb</t>
         </is>
       </c>
-      <c r="H39" s="3" t="n">
+      <c r="H39" s="6" t="n">
         <v>35</v>
       </c>
-      <c r="I39" s="3" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr"/>
-      <c r="K39" s="4" t="n">
+      <c r="I39" s="6" t="inlineStr"/>
+      <c r="J39" s="5" t="inlineStr"/>
+      <c r="K39" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="L39" s="2" t="inlineStr">
+      <c r="L39" s="5" t="inlineStr">
         <is>
           <t>20 GB de franquia 2 Meses de YouTube ilimitado</t>
         </is>
       </c>
-      <c r="M39" s="2" t="inlineStr"/>
-      <c r="N39" s="2" t="inlineStr"/>
-      <c r="O39" s="2" t="inlineStr"/>
-      <c r="P39" s="2" t="inlineStr"/>
-      <c r="Q39" s="2" t="inlineStr"/>
-      <c r="R39" s="2" t="inlineStr"/>
-      <c r="S39" s="2" t="inlineStr">
+      <c r="M39" s="5" t="inlineStr"/>
+      <c r="N39" s="5" t="inlineStr"/>
+      <c r="O39" s="5" t="inlineStr"/>
+      <c r="P39" s="5" t="inlineStr"/>
+      <c r="Q39" s="5" t="inlineStr"/>
+      <c r="R39" s="5" t="inlineStr"/>
+      <c r="S39" s="5" t="inlineStr">
         <is>
           <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/easy-lite</t>
         </is>
       </c>
-      <c r="T39" s="2" t="inlineStr">
+      <c r="T39" s="5" t="inlineStr">
         <is>
           <t>data/raw/vivo_lite_SP.html</t>
         </is>
@@ -3140,7 +4082,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3195,62 +4137,62 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>vivo</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>lite</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>Easy Lite</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G41" s="5" t="inlineStr">
         <is>
           <t>vivo:VIV202600019129-40gb</t>
         </is>
       </c>
-      <c r="H41" s="3" t="n">
+      <c r="H41" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="I41" s="3" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr"/>
-      <c r="K41" s="4" t="n">
+      <c r="I41" s="6" t="inlineStr"/>
+      <c r="J41" s="5" t="inlineStr"/>
+      <c r="K41" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="L41" s="2" t="inlineStr"/>
-      <c r="M41" s="2" t="inlineStr"/>
-      <c r="N41" s="2" t="inlineStr"/>
-      <c r="O41" s="2" t="inlineStr"/>
-      <c r="P41" s="2" t="inlineStr"/>
-      <c r="Q41" s="2" t="inlineStr"/>
-      <c r="R41" s="2" t="inlineStr"/>
-      <c r="S41" s="2" t="inlineStr">
+      <c r="L41" s="5" t="inlineStr"/>
+      <c r="M41" s="5" t="inlineStr"/>
+      <c r="N41" s="5" t="inlineStr"/>
+      <c r="O41" s="5" t="inlineStr"/>
+      <c r="P41" s="5" t="inlineStr"/>
+      <c r="Q41" s="5" t="inlineStr"/>
+      <c r="R41" s="5" t="inlineStr"/>
+      <c r="S41" s="5" t="inlineStr">
         <is>
           <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/easy-lite</t>
         </is>
       </c>
-      <c r="T41" s="2" t="inlineStr">
+      <c r="T41" s="5" t="inlineStr">
         <is>
           <t>data/raw/vivo_lite_SP.html</t>
         </is>
@@ -3264,7 +4206,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3327,74 +4269,74 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
         <is>
           <t>vivo</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>postpaid</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F43" s="5" t="inlineStr">
         <is>
           <t>Vivo Pós com Disney+</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G43" s="5" t="inlineStr">
         <is>
           <t>vivo:VIV202600022115-60gb</t>
         </is>
       </c>
-      <c r="H43" s="3" t="n">
+      <c r="H43" s="6" t="n">
         <v>180</v>
       </c>
-      <c r="I43" s="3" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr"/>
-      <c r="K43" s="4" t="n">
+      <c r="I43" s="6" t="inlineStr"/>
+      <c r="J43" s="5" t="inlineStr"/>
+      <c r="K43" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="L43" s="2" t="inlineStr">
+      <c r="L43" s="5" t="inlineStr">
         <is>
           <t>50 GB de franquia 10 GB de bônus</t>
         </is>
       </c>
-      <c r="M43" s="2" t="inlineStr"/>
-      <c r="N43" s="2" t="inlineStr"/>
-      <c r="O43" s="2" t="inlineStr"/>
-      <c r="P43" s="2" t="inlineStr">
+      <c r="M43" s="5" t="inlineStr"/>
+      <c r="N43" s="5" t="inlineStr"/>
+      <c r="O43" s="5" t="inlineStr"/>
+      <c r="P43" s="5" t="inlineStr">
         <is>
           <t>Disney+</t>
         </is>
       </c>
-      <c r="Q43" s="2" t="inlineStr"/>
-      <c r="R43" s="2" t="inlineStr">
+      <c r="Q43" s="5" t="inlineStr"/>
+      <c r="R43" s="5" t="inlineStr">
         <is>
           <t>Assinatura Disney+ Padrão inclusa</t>
         </is>
       </c>
-      <c r="S43" s="2" t="inlineStr">
+      <c r="S43" s="5" t="inlineStr">
         <is>
           <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
         </is>
       </c>
-      <c r="T43" s="2" t="inlineStr">
+      <c r="T43" s="5" t="inlineStr">
         <is>
           <t>data/raw/vivo_postpaid_SP.html</t>
         </is>
@@ -3408,7 +4350,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3475,74 +4417,74 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
         <is>
           <t>vivo</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>postpaid</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E45" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F45" s="5" t="inlineStr">
         <is>
           <t>Vivo Pós com Netflix</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G45" s="5" t="inlineStr">
         <is>
           <t>vivo:VIV202600029234-60gb</t>
         </is>
       </c>
-      <c r="H45" s="3" t="n">
+      <c r="H45" s="6" t="n">
         <v>180</v>
       </c>
-      <c r="I45" s="3" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr"/>
-      <c r="K45" s="4" t="n">
+      <c r="I45" s="6" t="inlineStr"/>
+      <c r="J45" s="5" t="inlineStr"/>
+      <c r="K45" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="L45" s="2" t="inlineStr">
+      <c r="L45" s="5" t="inlineStr">
         <is>
           <t>50 GB de franquia 10 GB de bônus</t>
         </is>
       </c>
-      <c r="M45" s="2" t="inlineStr"/>
-      <c r="N45" s="2" t="inlineStr"/>
-      <c r="O45" s="2" t="inlineStr"/>
-      <c r="P45" s="2" t="inlineStr">
+      <c r="M45" s="5" t="inlineStr"/>
+      <c r="N45" s="5" t="inlineStr"/>
+      <c r="O45" s="5" t="inlineStr"/>
+      <c r="P45" s="5" t="inlineStr">
         <is>
           <t>Netflix</t>
         </is>
       </c>
-      <c r="Q45" s="2" t="inlineStr"/>
-      <c r="R45" s="2" t="inlineStr">
+      <c r="Q45" s="5" t="inlineStr"/>
+      <c r="R45" s="5" t="inlineStr">
         <is>
           <t>Assinatura Netflix Padrão inclusa</t>
         </is>
       </c>
-      <c r="S45" s="2" t="inlineStr">
+      <c r="S45" s="5" t="inlineStr">
         <is>
           <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
         </is>
       </c>
-      <c r="T45" s="2" t="inlineStr">
+      <c r="T45" s="5" t="inlineStr">
         <is>
           <t>data/raw/vivo_postpaid_SP.html</t>
         </is>
@@ -3556,7 +4498,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3623,74 +4565,74 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
         <is>
           <t>vivo</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>postpaid</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E47" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F47" s="5" t="inlineStr">
         <is>
           <t>Vivo Pós com Spotify</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G47" s="5" t="inlineStr">
         <is>
           <t>vivo:VIV202600029229-60gb</t>
         </is>
       </c>
-      <c r="H47" s="3" t="n">
+      <c r="H47" s="6" t="n">
         <v>165</v>
       </c>
-      <c r="I47" s="3" t="inlineStr"/>
-      <c r="J47" s="2" t="inlineStr"/>
-      <c r="K47" s="4" t="n">
+      <c r="I47" s="6" t="inlineStr"/>
+      <c r="J47" s="5" t="inlineStr"/>
+      <c r="K47" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="L47" s="2" t="inlineStr">
+      <c r="L47" s="5" t="inlineStr">
         <is>
           <t>50 GB de franquia 10 GB de bônus</t>
         </is>
       </c>
-      <c r="M47" s="2" t="inlineStr"/>
-      <c r="N47" s="2" t="inlineStr"/>
-      <c r="O47" s="2" t="inlineStr"/>
-      <c r="P47" s="2" t="inlineStr">
+      <c r="M47" s="5" t="inlineStr"/>
+      <c r="N47" s="5" t="inlineStr"/>
+      <c r="O47" s="5" t="inlineStr"/>
+      <c r="P47" s="5" t="inlineStr">
         <is>
           <t>Spotify</t>
         </is>
       </c>
-      <c r="Q47" s="2" t="inlineStr"/>
-      <c r="R47" s="2" t="inlineStr">
+      <c r="Q47" s="5" t="inlineStr"/>
+      <c r="R47" s="5" t="inlineStr">
         <is>
           <t>Assinatura Spotify Premium inclusa</t>
         </is>
       </c>
-      <c r="S47" s="2" t="inlineStr">
+      <c r="S47" s="5" t="inlineStr">
         <is>
           <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
         </is>
       </c>
-      <c r="T47" s="2" t="inlineStr">
+      <c r="T47" s="5" t="inlineStr">
         <is>
           <t>data/raw/vivo_postpaid_SP.html</t>
         </is>
@@ -3704,7 +4646,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -3767,66 +4709,66 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
         <is>
           <t>vivo</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>prepaid</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E49" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F49" s="5" t="inlineStr">
         <is>
           <t>Vivo Pré</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G49" s="5" t="inlineStr">
         <is>
           <t>vivo:VIV202600022379-25gb</t>
         </is>
       </c>
-      <c r="H49" s="3" t="n">
+      <c r="H49" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="I49" s="3" t="inlineStr"/>
-      <c r="J49" s="2" t="inlineStr"/>
-      <c r="K49" s="4" t="n">
+      <c r="I49" s="6" t="inlineStr"/>
+      <c r="J49" s="5" t="inlineStr"/>
+      <c r="K49" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="L49" s="2" t="inlineStr">
+      <c r="L49" s="5" t="inlineStr">
         <is>
           <t>15 GB para navegar como quiser 5 GB de bônus 5 GB para navegar no Youtube</t>
         </is>
       </c>
-      <c r="M49" s="2" t="inlineStr"/>
-      <c r="N49" s="2" t="inlineStr"/>
-      <c r="O49" s="2" t="inlineStr"/>
-      <c r="P49" s="2" t="inlineStr"/>
-      <c r="Q49" s="2" t="inlineStr"/>
-      <c r="R49" s="2" t="inlineStr"/>
-      <c r="S49" s="2" t="inlineStr">
+      <c r="M49" s="5" t="inlineStr"/>
+      <c r="N49" s="5" t="inlineStr"/>
+      <c r="O49" s="5" t="inlineStr"/>
+      <c r="P49" s="5" t="inlineStr"/>
+      <c r="Q49" s="5" t="inlineStr"/>
+      <c r="R49" s="5" t="inlineStr"/>
+      <c r="S49" s="5" t="inlineStr">
         <is>
           <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/pre-pago/vivo-pre</t>
         </is>
       </c>
-      <c r="T49" s="2" t="inlineStr">
+      <c r="T49" s="5" t="inlineStr">
         <is>
           <t>data/raw/vivo_prepaid_SP.html</t>
         </is>
@@ -3840,7 +4782,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -3899,66 +4841,66 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
         <is>
           <t>vivo</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>prepaid</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E51" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F51" s="5" t="inlineStr">
         <is>
           <t>Vivo Pré</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G51" s="5" t="inlineStr">
         <is>
           <t>vivo:VIV202600022379-5gb</t>
         </is>
       </c>
-      <c r="H51" s="3" t="n">
+      <c r="H51" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="I51" s="3" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr"/>
-      <c r="K51" s="4" t="n">
+      <c r="I51" s="6" t="inlineStr"/>
+      <c r="J51" s="5" t="inlineStr"/>
+      <c r="K51" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="L51" s="2" t="inlineStr">
+      <c r="L51" s="5" t="inlineStr">
         <is>
           <t>5 GB para navegar como quiser</t>
         </is>
       </c>
-      <c r="M51" s="2" t="inlineStr"/>
-      <c r="N51" s="2" t="inlineStr"/>
-      <c r="O51" s="2" t="inlineStr"/>
-      <c r="P51" s="2" t="inlineStr"/>
-      <c r="Q51" s="2" t="inlineStr"/>
-      <c r="R51" s="2" t="inlineStr"/>
-      <c r="S51" s="2" t="inlineStr">
+      <c r="M51" s="5" t="inlineStr"/>
+      <c r="N51" s="5" t="inlineStr"/>
+      <c r="O51" s="5" t="inlineStr"/>
+      <c r="P51" s="5" t="inlineStr"/>
+      <c r="Q51" s="5" t="inlineStr"/>
+      <c r="R51" s="5" t="inlineStr"/>
+      <c r="S51" s="5" t="inlineStr">
         <is>
           <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/pre-pago/vivo-pre</t>
         </is>
       </c>
-      <c r="T51" s="2" t="inlineStr">
+      <c r="T51" s="5" t="inlineStr">
         <is>
           <t>data/raw/vivo_prepaid_SP.html</t>
         </is>
@@ -3972,7 +4914,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4039,6 +4981,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="008A8A8A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -4177,7 +5120,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -4246,70 +5189,70 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>claro</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>Controle 30GB</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>claro:plano-controle-30gb</t>
         </is>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="H3" s="6" t="n">
         <v>69.90000000000001</v>
       </c>
-      <c r="I3" s="3" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="4" t="n">
+      <c r="I3" s="6" t="inlineStr"/>
+      <c r="J3" s="5" t="inlineStr"/>
+      <c r="K3" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="L3" s="5" t="inlineStr"/>
+      <c r="M3" s="5" t="inlineStr">
         <is>
           <t>WhatsApp</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr"/>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="2" t="inlineStr">
+      <c r="N3" s="5" t="inlineStr"/>
+      <c r="O3" s="5" t="inlineStr"/>
+      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr"/>
+      <c r="R3" s="5" t="inlineStr">
         <is>
           <t>Para uso livre; Bônus do Hexa para uso livre; Bônus para redes sociais e apps; Redes sociais e apps; WhatsApp ilimitado</t>
         </is>
       </c>
-      <c r="S3" s="2" t="inlineStr">
+      <c r="S3" s="5" t="inlineStr">
         <is>
           <t>https://www.claro.com.br/celular/controle</t>
         </is>
       </c>
-      <c r="T3" s="2" t="inlineStr">
+      <c r="T3" s="5" t="inlineStr">
         <is>
           <t>data/raw/claro_control_SP.json</t>
         </is>
@@ -4323,7 +5266,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -4386,70 +5329,70 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>claro</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>flex</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Flex 15GB</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>claro:plano-flex-15gb</t>
         </is>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="H5" s="6" t="n">
         <v>44.9</v>
       </c>
-      <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="4" t="n">
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="5" t="inlineStr"/>
+      <c r="K5" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="L5" s="5" t="inlineStr"/>
+      <c r="M5" s="5" t="inlineStr">
         <is>
           <t>WhatsApp</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr"/>
-      <c r="O5" s="2" t="inlineStr"/>
-      <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr"/>
-      <c r="R5" s="2" t="inlineStr">
+      <c r="N5" s="5" t="inlineStr"/>
+      <c r="O5" s="5" t="inlineStr"/>
+      <c r="P5" s="5" t="inlineStr"/>
+      <c r="Q5" s="5" t="inlineStr"/>
+      <c r="R5" s="5" t="inlineStr">
         <is>
           <t>Para uso livre; Bônus do Hexa para uso livre; Para redes sociais e apps; Bônus extra nos apps; WhatsApp ilimitado</t>
         </is>
       </c>
-      <c r="S5" s="2" t="inlineStr">
+      <c r="S5" s="5" t="inlineStr">
         <is>
           <t>https://www.claro.com.br/celular/flex</t>
         </is>
       </c>
-      <c r="T5" s="2" t="inlineStr">
+      <c r="T5" s="5" t="inlineStr">
         <is>
           <t>data/raw/claro_flex_SP.json</t>
         </is>
@@ -4463,7 +5406,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -4526,70 +5469,70 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>claro</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>flex</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>Flex 30GB</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>claro:plano-flex-30gb</t>
         </is>
       </c>
-      <c r="H7" s="3" t="n">
+      <c r="H7" s="6" t="n">
         <v>69.90000000000001</v>
       </c>
-      <c r="I7" s="3" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="4" t="n">
+      <c r="I7" s="6" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr"/>
+      <c r="K7" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="L7" s="5" t="inlineStr"/>
+      <c r="M7" s="5" t="inlineStr">
         <is>
           <t>WhatsApp</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr"/>
-      <c r="O7" s="2" t="inlineStr"/>
-      <c r="P7" s="2" t="inlineStr"/>
-      <c r="Q7" s="2" t="inlineStr"/>
-      <c r="R7" s="2" t="inlineStr">
+      <c r="N7" s="5" t="inlineStr"/>
+      <c r="O7" s="5" t="inlineStr"/>
+      <c r="P7" s="5" t="inlineStr"/>
+      <c r="Q7" s="5" t="inlineStr"/>
+      <c r="R7" s="5" t="inlineStr">
         <is>
           <t>Para uso livre; Bônus do Hexa para uso livre; Para redes sociais e apps; Bônus extra nos apps; WhatsApp ilimitado; Assinatura Claro musica inclusa</t>
         </is>
       </c>
-      <c r="S7" s="2" t="inlineStr">
+      <c r="S7" s="5" t="inlineStr">
         <is>
           <t>https://www.claro.com.br/celular/flex</t>
         </is>
       </c>
-      <c r="T7" s="2" t="inlineStr">
+      <c r="T7" s="5" t="inlineStr">
         <is>
           <t>data/raw/claro_flex_SP.json</t>
         </is>
@@ -4603,7 +5546,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -4666,70 +5609,70 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>claro</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>postpaid</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>Pós 100GB</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>claro:plano-pos-100gb</t>
         </is>
       </c>
-      <c r="H9" s="3" t="n">
+      <c r="H9" s="6" t="n">
         <v>179.9</v>
       </c>
-      <c r="I9" s="3" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="4" t="n">
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr"/>
+      <c r="K9" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="L9" s="5" t="inlineStr"/>
+      <c r="M9" s="5" t="inlineStr">
         <is>
           <t>WhatsApp</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr"/>
-      <c r="O9" s="2" t="inlineStr"/>
-      <c r="P9" s="2" t="inlineStr"/>
-      <c r="Q9" s="2" t="inlineStr"/>
-      <c r="R9" s="2" t="inlineStr">
+      <c r="N9" s="5" t="inlineStr"/>
+      <c r="O9" s="5" t="inlineStr"/>
+      <c r="P9" s="5" t="inlineStr"/>
+      <c r="Q9" s="5" t="inlineStr"/>
+      <c r="R9" s="5" t="inlineStr">
         <is>
           <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Américas; Claro Sync: Smartwatch conectado</t>
         </is>
       </c>
-      <c r="S9" s="2" t="inlineStr">
+      <c r="S9" s="5" t="inlineStr">
         <is>
           <t>https://www.claro.com.br/celular/pos</t>
         </is>
       </c>
-      <c r="T9" s="2" t="inlineStr">
+      <c r="T9" s="5" t="inlineStr">
         <is>
           <t>data/raw/claro_postpaid_SP.json</t>
         </is>
@@ -4743,7 +5686,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -4806,70 +5749,70 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>claro</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>postpaid</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>Pós 200GB</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>claro:plano-pos-200gb</t>
         </is>
       </c>
-      <c r="H11" s="3" t="n">
+      <c r="H11" s="6" t="n">
         <v>339.9</v>
       </c>
-      <c r="I11" s="3" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="4" t="n">
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="5" t="inlineStr"/>
+      <c r="K11" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="L11" s="5" t="inlineStr"/>
+      <c r="M11" s="5" t="inlineStr">
         <is>
           <t>WhatsApp</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr"/>
-      <c r="O11" s="2" t="inlineStr"/>
-      <c r="P11" s="2" t="inlineStr"/>
-      <c r="Q11" s="2" t="inlineStr"/>
-      <c r="R11" s="2" t="inlineStr">
+      <c r="N11" s="5" t="inlineStr"/>
+      <c r="O11" s="5" t="inlineStr"/>
+      <c r="P11" s="5" t="inlineStr"/>
+      <c r="Q11" s="5" t="inlineStr"/>
+      <c r="R11" s="5" t="inlineStr">
         <is>
           <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Mundo; Claro Sync: Smartwatch conectado</t>
         </is>
       </c>
-      <c r="S11" s="2" t="inlineStr">
+      <c r="S11" s="5" t="inlineStr">
         <is>
           <t>https://www.claro.com.br/celular/pos</t>
         </is>
       </c>
-      <c r="T11" s="2" t="inlineStr">
+      <c r="T11" s="5" t="inlineStr">
         <is>
           <t>data/raw/claro_postpaid_SP.json</t>
         </is>
@@ -4883,7 +5826,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -4946,70 +5889,70 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>claro</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>postpaid</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>Pós 60GB</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>claro:plano-pos-60gb</t>
         </is>
       </c>
-      <c r="H13" s="3" t="n">
+      <c r="H13" s="6" t="n">
         <v>124.9</v>
       </c>
-      <c r="I13" s="3" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="4" t="n">
+      <c r="I13" s="6" t="inlineStr"/>
+      <c r="J13" s="5" t="inlineStr"/>
+      <c r="K13" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="L13" s="2" t="inlineStr"/>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="L13" s="5" t="inlineStr"/>
+      <c r="M13" s="5" t="inlineStr">
         <is>
           <t>WhatsApp</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr"/>
-      <c r="O13" s="2" t="inlineStr"/>
-      <c r="P13" s="2" t="inlineStr"/>
-      <c r="Q13" s="2" t="inlineStr"/>
-      <c r="R13" s="2" t="inlineStr">
+      <c r="N13" s="5" t="inlineStr"/>
+      <c r="O13" s="5" t="inlineStr"/>
+      <c r="P13" s="5" t="inlineStr"/>
+      <c r="Q13" s="5" t="inlineStr"/>
+      <c r="R13" s="5" t="inlineStr">
         <is>
           <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Américas; Claro Sync: Smartwatch conectado</t>
         </is>
       </c>
-      <c r="S13" s="2" t="inlineStr">
+      <c r="S13" s="5" t="inlineStr">
         <is>
           <t>https://www.claro.com.br/celular/pos</t>
         </is>
       </c>
-      <c r="T13" s="2" t="inlineStr">
+      <c r="T13" s="5" t="inlineStr">
         <is>
           <t>data/raw/claro_postpaid_SP.json</t>
         </is>
@@ -5023,7 +5966,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -5082,62 +6025,62 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>tim</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>TIM Controle 41GB</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>tim:162901</t>
         </is>
       </c>
-      <c r="H15" s="3" t="n">
+      <c r="H15" s="6" t="n">
         <v>58.99</v>
       </c>
-      <c r="I15" s="3" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="4" t="n">
+      <c r="I15" s="6" t="inlineStr"/>
+      <c r="J15" s="5" t="inlineStr"/>
+      <c r="K15" s="7" t="n">
         <v>41</v>
       </c>
-      <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="2" t="inlineStr"/>
-      <c r="N15" s="2" t="inlineStr"/>
-      <c r="O15" s="2" t="inlineStr"/>
-      <c r="P15" s="2" t="inlineStr"/>
-      <c r="Q15" s="2" t="inlineStr"/>
-      <c r="R15" s="2" t="inlineStr"/>
-      <c r="S15" s="2" t="inlineStr">
+      <c r="L15" s="5" t="inlineStr"/>
+      <c r="M15" s="5" t="inlineStr"/>
+      <c r="N15" s="5" t="inlineStr"/>
+      <c r="O15" s="5" t="inlineStr"/>
+      <c r="P15" s="5" t="inlineStr"/>
+      <c r="Q15" s="5" t="inlineStr"/>
+      <c r="R15" s="5" t="inlineStr"/>
+      <c r="S15" s="5" t="inlineStr">
         <is>
           <t>https://www.tim.com.br/sp/para-voce/planos/controle</t>
         </is>
       </c>
-      <c r="T15" s="2" t="inlineStr">
+      <c r="T15" s="5" t="inlineStr">
         <is>
           <t>data/raw/tim_control_SP.html</t>
         </is>
@@ -5151,7 +6094,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -5206,62 +6149,62 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>tim</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>TIM Controle Plus 45GB</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>tim:155891</t>
         </is>
       </c>
-      <c r="H17" s="3" t="n">
+      <c r="H17" s="6" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="I17" s="3" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="4" t="n">
+      <c r="I17" s="6" t="inlineStr"/>
+      <c r="J17" s="5" t="inlineStr"/>
+      <c r="K17" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="2" t="inlineStr"/>
-      <c r="N17" s="2" t="inlineStr"/>
-      <c r="O17" s="2" t="inlineStr"/>
-      <c r="P17" s="2" t="inlineStr"/>
-      <c r="Q17" s="2" t="inlineStr"/>
-      <c r="R17" s="2" t="inlineStr"/>
-      <c r="S17" s="2" t="inlineStr">
+      <c r="L17" s="5" t="inlineStr"/>
+      <c r="M17" s="5" t="inlineStr"/>
+      <c r="N17" s="5" t="inlineStr"/>
+      <c r="O17" s="5" t="inlineStr"/>
+      <c r="P17" s="5" t="inlineStr"/>
+      <c r="Q17" s="5" t="inlineStr"/>
+      <c r="R17" s="5" t="inlineStr"/>
+      <c r="S17" s="5" t="inlineStr">
         <is>
           <t>https://www.tim.com.br/sp/para-voce/planos/controle</t>
         </is>
       </c>
-      <c r="T17" s="2" t="inlineStr">
+      <c r="T17" s="5" t="inlineStr">
         <is>
           <t>data/raw/tim_control_SP.html</t>
         </is>
@@ -5275,7 +6218,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -5330,60 +6273,60 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>tim</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>TIM Controle Pro Express</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>tim:143576</t>
         </is>
       </c>
-      <c r="H19" s="3" t="n">
+      <c r="H19" s="6" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="I19" s="3" t="inlineStr"/>
-      <c r="J19" s="2" t="inlineStr"/>
-      <c r="K19" s="4" t="inlineStr"/>
-      <c r="L19" s="2" t="inlineStr"/>
-      <c r="M19" s="2" t="inlineStr"/>
-      <c r="N19" s="2" t="inlineStr"/>
-      <c r="O19" s="2" t="inlineStr"/>
-      <c r="P19" s="2" t="inlineStr"/>
-      <c r="Q19" s="2" t="inlineStr"/>
-      <c r="R19" s="2" t="inlineStr"/>
-      <c r="S19" s="2" t="inlineStr">
+      <c r="I19" s="6" t="inlineStr"/>
+      <c r="J19" s="5" t="inlineStr"/>
+      <c r="K19" s="7" t="inlineStr"/>
+      <c r="L19" s="5" t="inlineStr"/>
+      <c r="M19" s="5" t="inlineStr"/>
+      <c r="N19" s="5" t="inlineStr"/>
+      <c r="O19" s="5" t="inlineStr"/>
+      <c r="P19" s="5" t="inlineStr"/>
+      <c r="Q19" s="5" t="inlineStr"/>
+      <c r="R19" s="5" t="inlineStr"/>
+      <c r="S19" s="5" t="inlineStr">
         <is>
           <t>https://www.tim.com.br/sp/para-voce/planos/controle</t>
         </is>
       </c>
-      <c r="T19" s="2" t="inlineStr">
+      <c r="T19" s="5" t="inlineStr">
         <is>
           <t>data/raw/tim_control_SP.html</t>
         </is>
@@ -5397,7 +6340,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -5452,62 +6395,62 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>tim</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>postpaid</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>TIM Black A Express 67GB</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>tim:55121</t>
         </is>
       </c>
-      <c r="H21" s="3" t="n">
+      <c r="H21" s="6" t="n">
         <v>119.99</v>
       </c>
-      <c r="I21" s="3" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr"/>
-      <c r="K21" s="4" t="n">
+      <c r="I21" s="6" t="inlineStr"/>
+      <c r="J21" s="5" t="inlineStr"/>
+      <c r="K21" s="7" t="n">
         <v>67</v>
       </c>
-      <c r="L21" s="2" t="inlineStr"/>
-      <c r="M21" s="2" t="inlineStr"/>
-      <c r="N21" s="2" t="inlineStr"/>
-      <c r="O21" s="2" t="inlineStr"/>
-      <c r="P21" s="2" t="inlineStr"/>
-      <c r="Q21" s="2" t="inlineStr"/>
-      <c r="R21" s="2" t="inlineStr"/>
-      <c r="S21" s="2" t="inlineStr">
+      <c r="L21" s="5" t="inlineStr"/>
+      <c r="M21" s="5" t="inlineStr"/>
+      <c r="N21" s="5" t="inlineStr"/>
+      <c r="O21" s="5" t="inlineStr"/>
+      <c r="P21" s="5" t="inlineStr"/>
+      <c r="Q21" s="5" t="inlineStr"/>
+      <c r="R21" s="5" t="inlineStr"/>
+      <c r="S21" s="5" t="inlineStr">
         <is>
           <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
         </is>
       </c>
-      <c r="T21" s="2" t="inlineStr">
+      <c r="T21" s="5" t="inlineStr">
         <is>
           <t>data/raw/tim_postpaid_SP.html</t>
         </is>
@@ -5521,7 +6464,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -5576,62 +6519,62 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>tim</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>postpaid</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>TIM Black C Express 107GB</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>tim:52151</t>
         </is>
       </c>
-      <c r="H23" s="3" t="n">
+      <c r="H23" s="6" t="n">
         <v>164.99</v>
       </c>
-      <c r="I23" s="3" t="inlineStr"/>
-      <c r="J23" s="2" t="inlineStr"/>
-      <c r="K23" s="4" t="n">
+      <c r="I23" s="6" t="inlineStr"/>
+      <c r="J23" s="5" t="inlineStr"/>
+      <c r="K23" s="7" t="n">
         <v>107</v>
       </c>
-      <c r="L23" s="2" t="inlineStr"/>
-      <c r="M23" s="2" t="inlineStr"/>
-      <c r="N23" s="2" t="inlineStr"/>
-      <c r="O23" s="2" t="inlineStr"/>
-      <c r="P23" s="2" t="inlineStr"/>
-      <c r="Q23" s="2" t="inlineStr"/>
-      <c r="R23" s="2" t="inlineStr"/>
-      <c r="S23" s="2" t="inlineStr">
+      <c r="L23" s="5" t="inlineStr"/>
+      <c r="M23" s="5" t="inlineStr"/>
+      <c r="N23" s="5" t="inlineStr"/>
+      <c r="O23" s="5" t="inlineStr"/>
+      <c r="P23" s="5" t="inlineStr"/>
+      <c r="Q23" s="5" t="inlineStr"/>
+      <c r="R23" s="5" t="inlineStr"/>
+      <c r="S23" s="5" t="inlineStr">
         <is>
           <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
         </is>
       </c>
-      <c r="T23" s="2" t="inlineStr">
+      <c r="T23" s="5" t="inlineStr">
         <is>
           <t>data/raw/tim_postpaid_SP.html</t>
         </is>
@@ -5645,7 +6588,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -5700,62 +6643,62 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>tim</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>postpaid</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>TIM Black Plus 80GB</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>tim:54256</t>
         </is>
       </c>
-      <c r="H25" s="3" t="n">
+      <c r="H25" s="6" t="n">
         <v>149.99</v>
       </c>
-      <c r="I25" s="3" t="inlineStr"/>
-      <c r="J25" s="2" t="inlineStr"/>
-      <c r="K25" s="4" t="n">
+      <c r="I25" s="6" t="inlineStr"/>
+      <c r="J25" s="5" t="inlineStr"/>
+      <c r="K25" s="7" t="n">
         <v>80</v>
       </c>
-      <c r="L25" s="2" t="inlineStr"/>
-      <c r="M25" s="2" t="inlineStr"/>
-      <c r="N25" s="2" t="inlineStr"/>
-      <c r="O25" s="2" t="inlineStr"/>
-      <c r="P25" s="2" t="inlineStr"/>
-      <c r="Q25" s="2" t="inlineStr"/>
-      <c r="R25" s="2" t="inlineStr"/>
-      <c r="S25" s="2" t="inlineStr">
+      <c r="L25" s="5" t="inlineStr"/>
+      <c r="M25" s="5" t="inlineStr"/>
+      <c r="N25" s="5" t="inlineStr"/>
+      <c r="O25" s="5" t="inlineStr"/>
+      <c r="P25" s="5" t="inlineStr"/>
+      <c r="Q25" s="5" t="inlineStr"/>
+      <c r="R25" s="5" t="inlineStr"/>
+      <c r="S25" s="5" t="inlineStr">
         <is>
           <t>https://www.tim.com.br/sp/para-voce/planos/pos-pago/tim-black</t>
         </is>
       </c>
-      <c r="T25" s="2" t="inlineStr">
+      <c r="T25" s="5" t="inlineStr">
         <is>
           <t>data/raw/tim_postpaid_SP.html</t>
         </is>
@@ -5769,7 +6712,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -5824,62 +6767,62 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>tim</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>prepaid</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>TIM Pré XIP Plus 16GB</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>tim:106306</t>
         </is>
       </c>
-      <c r="H27" s="3" t="n">
+      <c r="H27" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="I27" s="3" t="inlineStr"/>
-      <c r="J27" s="2" t="inlineStr"/>
-      <c r="K27" s="4" t="n">
+      <c r="I27" s="6" t="inlineStr"/>
+      <c r="J27" s="5" t="inlineStr"/>
+      <c r="K27" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="L27" s="2" t="inlineStr"/>
-      <c r="M27" s="2" t="inlineStr"/>
-      <c r="N27" s="2" t="inlineStr"/>
-      <c r="O27" s="2" t="inlineStr"/>
-      <c r="P27" s="2" t="inlineStr"/>
-      <c r="Q27" s="2" t="inlineStr"/>
-      <c r="R27" s="2" t="inlineStr"/>
-      <c r="S27" s="2" t="inlineStr">
+      <c r="L27" s="5" t="inlineStr"/>
+      <c r="M27" s="5" t="inlineStr"/>
+      <c r="N27" s="5" t="inlineStr"/>
+      <c r="O27" s="5" t="inlineStr"/>
+      <c r="P27" s="5" t="inlineStr"/>
+      <c r="Q27" s="5" t="inlineStr"/>
+      <c r="R27" s="5" t="inlineStr"/>
+      <c r="S27" s="5" t="inlineStr">
         <is>
           <t>https://www.tim.com.br/sp/para-voce/planos/pre-pago</t>
         </is>
       </c>
-      <c r="T27" s="2" t="inlineStr">
+      <c r="T27" s="5" t="inlineStr">
         <is>
           <t>data/raw/tim_prepaid_SP.html</t>
         </is>
@@ -5893,7 +6836,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -5948,62 +6891,62 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>tim</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>prepaid</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>TIM Pré XIP Plus 8GB</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>tim:59901</t>
         </is>
       </c>
-      <c r="H29" s="3" t="n">
+      <c r="H29" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="I29" s="3" t="inlineStr"/>
-      <c r="J29" s="2" t="inlineStr"/>
-      <c r="K29" s="4" t="n">
+      <c r="I29" s="6" t="inlineStr"/>
+      <c r="J29" s="5" t="inlineStr"/>
+      <c r="K29" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="L29" s="2" t="inlineStr"/>
-      <c r="M29" s="2" t="inlineStr"/>
-      <c r="N29" s="2" t="inlineStr"/>
-      <c r="O29" s="2" t="inlineStr"/>
-      <c r="P29" s="2" t="inlineStr"/>
-      <c r="Q29" s="2" t="inlineStr"/>
-      <c r="R29" s="2" t="inlineStr"/>
-      <c r="S29" s="2" t="inlineStr">
+      <c r="L29" s="5" t="inlineStr"/>
+      <c r="M29" s="5" t="inlineStr"/>
+      <c r="N29" s="5" t="inlineStr"/>
+      <c r="O29" s="5" t="inlineStr"/>
+      <c r="P29" s="5" t="inlineStr"/>
+      <c r="Q29" s="5" t="inlineStr"/>
+      <c r="R29" s="5" t="inlineStr"/>
+      <c r="S29" s="5" t="inlineStr">
         <is>
           <t>https://www.tim.com.br/sp/para-voce/planos/pre-pago</t>
         </is>
       </c>
-      <c r="T29" s="2" t="inlineStr">
+      <c r="T29" s="5" t="inlineStr">
         <is>
           <t>data/raw/tim_prepaid_SP.html</t>
         </is>
@@ -6017,7 +6960,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -6080,70 +7023,70 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>vivo</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>Vivo Controle</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>vivo:VIV202600029300-51gb</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="I31" s="3" t="inlineStr"/>
-      <c r="J31" s="2" t="inlineStr"/>
-      <c r="K31" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029300-61gb</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="I31" s="6" t="inlineStr"/>
+      <c r="J31" s="5" t="inlineStr"/>
+      <c r="K31" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
         <is>
           <t>20 GB de franquia 31 GB de bônus</t>
         </is>
       </c>
-      <c r="M31" s="2" t="inlineStr"/>
-      <c r="N31" s="2" t="inlineStr"/>
-      <c r="O31" s="2" t="inlineStr"/>
-      <c r="P31" s="2" t="inlineStr"/>
-      <c r="Q31" s="2" t="inlineStr"/>
-      <c r="R31" s="2" t="inlineStr">
+      <c r="M31" s="5" t="inlineStr"/>
+      <c r="N31" s="5" t="inlineStr"/>
+      <c r="O31" s="5" t="inlineStr"/>
+      <c r="P31" s="5" t="inlineStr"/>
+      <c r="Q31" s="5" t="inlineStr"/>
+      <c r="R31" s="5" t="inlineStr">
         <is>
           <t>6 meses grátis de Gemini com AI Plus</t>
         </is>
       </c>
-      <c r="S31" s="2" t="inlineStr">
+      <c r="S31" s="5" t="inlineStr">
         <is>
           <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
         </is>
       </c>
-      <c r="T31" s="2" t="inlineStr">
+      <c r="T31" s="5" t="inlineStr">
         <is>
           <t>data/raw/vivo_control_SP.html</t>
         </is>
@@ -6157,7 +7100,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -6182,16 +7125,16 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029273-51gb</t>
+          <t>vivo:VIV202600029273-61gb</t>
         </is>
       </c>
       <c r="H32" s="3" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="I32" s="3" t="inlineStr"/>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="4" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
@@ -6220,70 +7163,70 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>vivo</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>Vivo Controle Entretenimento</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>vivo:VIV202600029307-51gb</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="n">
-        <v>105</v>
-      </c>
-      <c r="I33" s="3" t="inlineStr"/>
-      <c r="J33" s="2" t="inlineStr"/>
-      <c r="K33" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029307-61gb</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>110</v>
+      </c>
+      <c r="I33" s="6" t="inlineStr"/>
+      <c r="J33" s="5" t="inlineStr"/>
+      <c r="K33" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
         <is>
           <t>20 GB de franquia 31 GB de bônus</t>
         </is>
       </c>
-      <c r="M33" s="2" t="inlineStr"/>
-      <c r="N33" s="2" t="inlineStr"/>
-      <c r="O33" s="2" t="inlineStr"/>
-      <c r="P33" s="2" t="inlineStr"/>
-      <c r="Q33" s="2" t="inlineStr"/>
-      <c r="R33" s="2" t="inlineStr">
+      <c r="M33" s="5" t="inlineStr"/>
+      <c r="N33" s="5" t="inlineStr"/>
+      <c r="O33" s="5" t="inlineStr"/>
+      <c r="P33" s="5" t="inlineStr"/>
+      <c r="Q33" s="5" t="inlineStr"/>
+      <c r="R33" s="5" t="inlineStr">
         <is>
           <t>Assinatura Vivo TV Inicial inclusa</t>
         </is>
       </c>
-      <c r="S33" s="2" t="inlineStr">
+      <c r="S33" s="5" t="inlineStr">
         <is>
           <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
         </is>
       </c>
-      <c r="T33" s="2" t="inlineStr">
+      <c r="T33" s="5" t="inlineStr">
         <is>
           <t>data/raw/vivo_control_SP.html</t>
         </is>
@@ -6297,7 +7240,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -6322,16 +7265,16 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029313-51gb</t>
+          <t>vivo:VIV202600029313-61gb</t>
         </is>
       </c>
       <c r="H34" s="3" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I34" s="3" t="inlineStr"/>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="4" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
@@ -6360,70 +7303,70 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>vivo</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>control</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>Vivo Controle Netflix</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>vivo:VIV202600029308-51gb</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="I35" s="3" t="inlineStr"/>
-      <c r="J35" s="2" t="inlineStr"/>
-      <c r="K35" s="4" t="n">
-        <v>51</v>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>vivo:VIV202600029308-61gb</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="n">
+        <v>95</v>
+      </c>
+      <c r="I35" s="6" t="inlineStr"/>
+      <c r="J35" s="5" t="inlineStr"/>
+      <c r="K35" s="7" t="n">
+        <v>61</v>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
         <is>
           <t>20 GB de franquia 31 GB de bônus</t>
         </is>
       </c>
-      <c r="M35" s="2" t="inlineStr"/>
-      <c r="N35" s="2" t="inlineStr"/>
-      <c r="O35" s="2" t="inlineStr"/>
-      <c r="P35" s="2" t="inlineStr"/>
-      <c r="Q35" s="2" t="inlineStr"/>
-      <c r="R35" s="2" t="inlineStr">
+      <c r="M35" s="5" t="inlineStr"/>
+      <c r="N35" s="5" t="inlineStr"/>
+      <c r="O35" s="5" t="inlineStr"/>
+      <c r="P35" s="5" t="inlineStr"/>
+      <c r="Q35" s="5" t="inlineStr"/>
+      <c r="R35" s="5" t="inlineStr">
         <is>
           <t>Assinatura Netflix Padrão com anúncios</t>
         </is>
       </c>
-      <c r="S35" s="2" t="inlineStr">
+      <c r="S35" s="5" t="inlineStr">
         <is>
           <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-controle</t>
         </is>
       </c>
-      <c r="T35" s="2" t="inlineStr">
+      <c r="T35" s="5" t="inlineStr">
         <is>
           <t>data/raw/vivo_control_SP.html</t>
         </is>
@@ -6437,7 +7380,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -6462,16 +7405,16 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>vivo:VIV202600029301-51gb</t>
+          <t>vivo:VIV202600029301-61gb</t>
         </is>
       </c>
       <c r="H36" s="3" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="I36" s="3" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="4" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
@@ -6500,66 +7443,66 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>vivo</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>lite</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>Easy Lite</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>vivo:VIV202600005312-30gb</t>
         </is>
       </c>
-      <c r="H37" s="3" t="n">
+      <c r="H37" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="I37" s="3" t="inlineStr"/>
-      <c r="J37" s="2" t="inlineStr"/>
-      <c r="K37" s="4" t="n">
+      <c r="I37" s="6" t="inlineStr"/>
+      <c r="J37" s="5" t="inlineStr"/>
+      <c r="K37" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="L37" s="2" t="inlineStr">
+      <c r="L37" s="5" t="inlineStr">
         <is>
           <t>30 GB de franquia 2 Meses de YouTube ilimitado</t>
         </is>
       </c>
-      <c r="M37" s="2" t="inlineStr"/>
-      <c r="N37" s="2" t="inlineStr"/>
-      <c r="O37" s="2" t="inlineStr"/>
-      <c r="P37" s="2" t="inlineStr"/>
-      <c r="Q37" s="2" t="inlineStr"/>
-      <c r="R37" s="2" t="inlineStr"/>
-      <c r="S37" s="2" t="inlineStr">
+      <c r="M37" s="5" t="inlineStr"/>
+      <c r="N37" s="5" t="inlineStr"/>
+      <c r="O37" s="5" t="inlineStr"/>
+      <c r="P37" s="5" t="inlineStr"/>
+      <c r="Q37" s="5" t="inlineStr"/>
+      <c r="R37" s="5" t="inlineStr"/>
+      <c r="S37" s="5" t="inlineStr">
         <is>
           <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/easy-lite</t>
         </is>
       </c>
-      <c r="T37" s="2" t="inlineStr">
+      <c r="T37" s="5" t="inlineStr">
         <is>
           <t>data/raw/vivo_lite_SP.html</t>
         </is>
@@ -6573,7 +7516,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -6632,66 +7575,66 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>vivo</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>lite</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>Easy Lite</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>vivo:VIV202600019132-20gb</t>
         </is>
       </c>
-      <c r="H39" s="3" t="n">
+      <c r="H39" s="6" t="n">
         <v>35</v>
       </c>
-      <c r="I39" s="3" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr"/>
-      <c r="K39" s="4" t="n">
+      <c r="I39" s="6" t="inlineStr"/>
+      <c r="J39" s="5" t="inlineStr"/>
+      <c r="K39" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="L39" s="2" t="inlineStr">
+      <c r="L39" s="5" t="inlineStr">
         <is>
           <t>20 GB de franquia 2 Meses de YouTube ilimitado</t>
         </is>
       </c>
-      <c r="M39" s="2" t="inlineStr"/>
-      <c r="N39" s="2" t="inlineStr"/>
-      <c r="O39" s="2" t="inlineStr"/>
-      <c r="P39" s="2" t="inlineStr"/>
-      <c r="Q39" s="2" t="inlineStr"/>
-      <c r="R39" s="2" t="inlineStr"/>
-      <c r="S39" s="2" t="inlineStr">
+      <c r="M39" s="5" t="inlineStr"/>
+      <c r="N39" s="5" t="inlineStr"/>
+      <c r="O39" s="5" t="inlineStr"/>
+      <c r="P39" s="5" t="inlineStr"/>
+      <c r="Q39" s="5" t="inlineStr"/>
+      <c r="R39" s="5" t="inlineStr"/>
+      <c r="S39" s="5" t="inlineStr">
         <is>
           <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/easy-lite</t>
         </is>
       </c>
-      <c r="T39" s="2" t="inlineStr">
+      <c r="T39" s="5" t="inlineStr">
         <is>
           <t>data/raw/vivo_lite_SP.html</t>
         </is>
@@ -6705,7 +7648,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -6760,62 +7703,62 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>vivo</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>lite</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>Easy Lite</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G41" s="5" t="inlineStr">
         <is>
           <t>vivo:VIV202600019129-40gb</t>
         </is>
       </c>
-      <c r="H41" s="3" t="n">
+      <c r="H41" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="I41" s="3" t="inlineStr"/>
-      <c r="J41" s="2" t="inlineStr"/>
-      <c r="K41" s="4" t="n">
+      <c r="I41" s="6" t="inlineStr"/>
+      <c r="J41" s="5" t="inlineStr"/>
+      <c r="K41" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="L41" s="2" t="inlineStr"/>
-      <c r="M41" s="2" t="inlineStr"/>
-      <c r="N41" s="2" t="inlineStr"/>
-      <c r="O41" s="2" t="inlineStr"/>
-      <c r="P41" s="2" t="inlineStr"/>
-      <c r="Q41" s="2" t="inlineStr"/>
-      <c r="R41" s="2" t="inlineStr"/>
-      <c r="S41" s="2" t="inlineStr">
+      <c r="L41" s="5" t="inlineStr"/>
+      <c r="M41" s="5" t="inlineStr"/>
+      <c r="N41" s="5" t="inlineStr"/>
+      <c r="O41" s="5" t="inlineStr"/>
+      <c r="P41" s="5" t="inlineStr"/>
+      <c r="Q41" s="5" t="inlineStr"/>
+      <c r="R41" s="5" t="inlineStr"/>
+      <c r="S41" s="5" t="inlineStr">
         <is>
           <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/easy-lite</t>
         </is>
       </c>
-      <c r="T41" s="2" t="inlineStr">
+      <c r="T41" s="5" t="inlineStr">
         <is>
           <t>data/raw/vivo_lite_SP.html</t>
         </is>
@@ -6829,7 +7772,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -6892,74 +7835,74 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
         <is>
           <t>vivo</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>postpaid</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F43" s="5" t="inlineStr">
         <is>
           <t>Vivo Pós com Disney+</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G43" s="5" t="inlineStr">
         <is>
           <t>vivo:VIV202600022115-60gb</t>
         </is>
       </c>
-      <c r="H43" s="3" t="n">
+      <c r="H43" s="6" t="n">
         <v>180</v>
       </c>
-      <c r="I43" s="3" t="inlineStr"/>
-      <c r="J43" s="2" t="inlineStr"/>
-      <c r="K43" s="4" t="n">
+      <c r="I43" s="6" t="inlineStr"/>
+      <c r="J43" s="5" t="inlineStr"/>
+      <c r="K43" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="L43" s="2" t="inlineStr">
+      <c r="L43" s="5" t="inlineStr">
         <is>
           <t>50 GB de franquia 10 GB de bônus</t>
         </is>
       </c>
-      <c r="M43" s="2" t="inlineStr"/>
-      <c r="N43" s="2" t="inlineStr"/>
-      <c r="O43" s="2" t="inlineStr"/>
-      <c r="P43" s="2" t="inlineStr">
+      <c r="M43" s="5" t="inlineStr"/>
+      <c r="N43" s="5" t="inlineStr"/>
+      <c r="O43" s="5" t="inlineStr"/>
+      <c r="P43" s="5" t="inlineStr">
         <is>
           <t>Disney+</t>
         </is>
       </c>
-      <c r="Q43" s="2" t="inlineStr"/>
-      <c r="R43" s="2" t="inlineStr">
+      <c r="Q43" s="5" t="inlineStr"/>
+      <c r="R43" s="5" t="inlineStr">
         <is>
           <t>Assinatura Disney+ Padrão inclusa</t>
         </is>
       </c>
-      <c r="S43" s="2" t="inlineStr">
+      <c r="S43" s="5" t="inlineStr">
         <is>
           <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
         </is>
       </c>
-      <c r="T43" s="2" t="inlineStr">
+      <c r="T43" s="5" t="inlineStr">
         <is>
           <t>data/raw/vivo_postpaid_SP.html</t>
         </is>
@@ -6973,7 +7916,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -7040,74 +7983,74 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
         <is>
           <t>vivo</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>postpaid</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E45" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F45" s="5" t="inlineStr">
         <is>
           <t>Vivo Pós com Netflix</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G45" s="5" t="inlineStr">
         <is>
           <t>vivo:VIV202600029234-60gb</t>
         </is>
       </c>
-      <c r="H45" s="3" t="n">
+      <c r="H45" s="6" t="n">
         <v>180</v>
       </c>
-      <c r="I45" s="3" t="inlineStr"/>
-      <c r="J45" s="2" t="inlineStr"/>
-      <c r="K45" s="4" t="n">
+      <c r="I45" s="6" t="inlineStr"/>
+      <c r="J45" s="5" t="inlineStr"/>
+      <c r="K45" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="L45" s="2" t="inlineStr">
+      <c r="L45" s="5" t="inlineStr">
         <is>
           <t>50 GB de franquia 10 GB de bônus</t>
         </is>
       </c>
-      <c r="M45" s="2" t="inlineStr"/>
-      <c r="N45" s="2" t="inlineStr"/>
-      <c r="O45" s="2" t="inlineStr"/>
-      <c r="P45" s="2" t="inlineStr">
+      <c r="M45" s="5" t="inlineStr"/>
+      <c r="N45" s="5" t="inlineStr"/>
+      <c r="O45" s="5" t="inlineStr"/>
+      <c r="P45" s="5" t="inlineStr">
         <is>
           <t>Netflix</t>
         </is>
       </c>
-      <c r="Q45" s="2" t="inlineStr"/>
-      <c r="R45" s="2" t="inlineStr">
+      <c r="Q45" s="5" t="inlineStr"/>
+      <c r="R45" s="5" t="inlineStr">
         <is>
           <t>Assinatura Netflix Padrão inclusa</t>
         </is>
       </c>
-      <c r="S45" s="2" t="inlineStr">
+      <c r="S45" s="5" t="inlineStr">
         <is>
           <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
         </is>
       </c>
-      <c r="T45" s="2" t="inlineStr">
+      <c r="T45" s="5" t="inlineStr">
         <is>
           <t>data/raw/vivo_postpaid_SP.html</t>
         </is>
@@ -7121,7 +8064,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -7188,74 +8131,74 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
         <is>
           <t>vivo</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>postpaid</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E47" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F47" s="5" t="inlineStr">
         <is>
           <t>Vivo Pós com Spotify</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G47" s="5" t="inlineStr">
         <is>
           <t>vivo:VIV202600029229-60gb</t>
         </is>
       </c>
-      <c r="H47" s="3" t="n">
+      <c r="H47" s="6" t="n">
         <v>165</v>
       </c>
-      <c r="I47" s="3" t="inlineStr"/>
-      <c r="J47" s="2" t="inlineStr"/>
-      <c r="K47" s="4" t="n">
+      <c r="I47" s="6" t="inlineStr"/>
+      <c r="J47" s="5" t="inlineStr"/>
+      <c r="K47" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="L47" s="2" t="inlineStr">
+      <c r="L47" s="5" t="inlineStr">
         <is>
           <t>50 GB de franquia 10 GB de bônus</t>
         </is>
       </c>
-      <c r="M47" s="2" t="inlineStr"/>
-      <c r="N47" s="2" t="inlineStr"/>
-      <c r="O47" s="2" t="inlineStr"/>
-      <c r="P47" s="2" t="inlineStr">
+      <c r="M47" s="5" t="inlineStr"/>
+      <c r="N47" s="5" t="inlineStr"/>
+      <c r="O47" s="5" t="inlineStr"/>
+      <c r="P47" s="5" t="inlineStr">
         <is>
           <t>Spotify</t>
         </is>
       </c>
-      <c r="Q47" s="2" t="inlineStr"/>
-      <c r="R47" s="2" t="inlineStr">
+      <c r="Q47" s="5" t="inlineStr"/>
+      <c r="R47" s="5" t="inlineStr">
         <is>
           <t>Assinatura Spotify Premium inclusa</t>
         </is>
       </c>
-      <c r="S47" s="2" t="inlineStr">
+      <c r="S47" s="5" t="inlineStr">
         <is>
           <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/planos-pos-pago</t>
         </is>
       </c>
-      <c r="T47" s="2" t="inlineStr">
+      <c r="T47" s="5" t="inlineStr">
         <is>
           <t>data/raw/vivo_postpaid_SP.html</t>
         </is>
@@ -7269,7 +8212,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -7332,66 +8275,66 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
         <is>
           <t>vivo</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>prepaid</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E49" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F49" s="5" t="inlineStr">
         <is>
           <t>Vivo Pré</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G49" s="5" t="inlineStr">
         <is>
           <t>vivo:VIV202600022379-25gb</t>
         </is>
       </c>
-      <c r="H49" s="3" t="n">
+      <c r="H49" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="I49" s="3" t="inlineStr"/>
-      <c r="J49" s="2" t="inlineStr"/>
-      <c r="K49" s="4" t="n">
+      <c r="I49" s="6" t="inlineStr"/>
+      <c r="J49" s="5" t="inlineStr"/>
+      <c r="K49" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="L49" s="2" t="inlineStr">
+      <c r="L49" s="5" t="inlineStr">
         <is>
           <t>15 GB para navegar como quiser 5 GB de bônus 5 GB para navegar no Youtube</t>
         </is>
       </c>
-      <c r="M49" s="2" t="inlineStr"/>
-      <c r="N49" s="2" t="inlineStr"/>
-      <c r="O49" s="2" t="inlineStr"/>
-      <c r="P49" s="2" t="inlineStr"/>
-      <c r="Q49" s="2" t="inlineStr"/>
-      <c r="R49" s="2" t="inlineStr"/>
-      <c r="S49" s="2" t="inlineStr">
+      <c r="M49" s="5" t="inlineStr"/>
+      <c r="N49" s="5" t="inlineStr"/>
+      <c r="O49" s="5" t="inlineStr"/>
+      <c r="P49" s="5" t="inlineStr"/>
+      <c r="Q49" s="5" t="inlineStr"/>
+      <c r="R49" s="5" t="inlineStr"/>
+      <c r="S49" s="5" t="inlineStr">
         <is>
           <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/pre-pago/vivo-pre</t>
         </is>
       </c>
-      <c r="T49" s="2" t="inlineStr">
+      <c r="T49" s="5" t="inlineStr">
         <is>
           <t>data/raw/vivo_prepaid_SP.html</t>
         </is>
@@ -7405,7 +8348,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -7464,66 +8407,66 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22T16:18:01</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>2026-06-22T18:35:49</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
         <is>
           <t>vivo</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>prepaid</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E51" s="5" t="inlineStr">
         <is>
           <t>SP</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F51" s="5" t="inlineStr">
         <is>
           <t>Vivo Pré</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G51" s="5" t="inlineStr">
         <is>
           <t>vivo:VIV202600022379-5gb</t>
         </is>
       </c>
-      <c r="H51" s="3" t="n">
+      <c r="H51" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="I51" s="3" t="inlineStr"/>
-      <c r="J51" s="2" t="inlineStr"/>
-      <c r="K51" s="4" t="n">
+      <c r="I51" s="6" t="inlineStr"/>
+      <c r="J51" s="5" t="inlineStr"/>
+      <c r="K51" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="L51" s="2" t="inlineStr">
+      <c r="L51" s="5" t="inlineStr">
         <is>
           <t>5 GB para navegar como quiser</t>
         </is>
       </c>
-      <c r="M51" s="2" t="inlineStr"/>
-      <c r="N51" s="2" t="inlineStr"/>
-      <c r="O51" s="2" t="inlineStr"/>
-      <c r="P51" s="2" t="inlineStr"/>
-      <c r="Q51" s="2" t="inlineStr"/>
-      <c r="R51" s="2" t="inlineStr"/>
-      <c r="S51" s="2" t="inlineStr">
+      <c r="M51" s="5" t="inlineStr"/>
+      <c r="N51" s="5" t="inlineStr"/>
+      <c r="O51" s="5" t="inlineStr"/>
+      <c r="P51" s="5" t="inlineStr"/>
+      <c r="Q51" s="5" t="inlineStr"/>
+      <c r="R51" s="5" t="inlineStr"/>
+      <c r="S51" s="5" t="inlineStr">
         <is>
           <t>https://vivo.com.br/para-voce/produtos-e-servicos/para-o-celular/pre-pago/vivo-pre</t>
         </is>
       </c>
-      <c r="T51" s="2" t="inlineStr">
+      <c r="T51" s="5" t="inlineStr">
         <is>
           <t>data/raw/vivo_prepaid_SP.html</t>
         </is>
@@ -7537,7 +8480,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -7597,6 +8540,23 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:T52"/>
+  <conditionalFormatting sqref="H2:H52">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I52">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>NOT(ISBLANK(I2))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7604,6 +8564,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="008A8A8A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -7669,7 +8630,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7677,6 +8637,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00102A43"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -7691,26 +8652,26 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>Mobile Price Tracker — Summary</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>Run timestamp</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T16:18:01</t>
+          <t>2026-06-22T18:35:49</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>Latest snapshot</t>
         </is>
@@ -7722,7 +8683,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>Plans in latest</t>
         </is>
@@ -7732,7 +8693,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>Snapshots in history</t>
         </is>
@@ -7742,27 +8703,27 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>carrier</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="1" t="inlineStr">
         <is>
           <t># plans</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>min price</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="1" t="inlineStr">
         <is>
           <t>avg price</t>
         </is>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="1" t="inlineStr">
         <is>
           <t>max price</t>
         </is>
@@ -7778,15 +8739,15 @@
         <f>COUNTIF(latest!$C$2:$C$2000,$A$9)</f>
         <v/>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="10">
         <f>IFERROR(_xlfn.MINIFS(latest!$H$2:$H$2000,latest!$C$2:$C$2000,$A$9),"-")</f>
         <v/>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="10">
         <f>IFERROR(AVERAGEIFS(latest!$H$2:$H$2000,latest!$C$2:$C$2000,$A$9),"-")</f>
         <v/>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="10">
         <f>IFERROR(_xlfn.MAXIFS(latest!$H$2:$H$2000,latest!$C$2:$C$2000,$A$9),"-")</f>
         <v/>
       </c>
@@ -7801,15 +8762,15 @@
         <f>COUNTIF(latest!$C$2:$C$2000,$A$10)</f>
         <v/>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="10">
         <f>IFERROR(_xlfn.MINIFS(latest!$H$2:$H$2000,latest!$C$2:$C$2000,$A$10),"-")</f>
         <v/>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="10">
         <f>IFERROR(AVERAGEIFS(latest!$H$2:$H$2000,latest!$C$2:$C$2000,$A$10),"-")</f>
         <v/>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="10">
         <f>IFERROR(_xlfn.MAXIFS(latest!$H$2:$H$2000,latest!$C$2:$C$2000,$A$10),"-")</f>
         <v/>
       </c>
@@ -7824,15 +8785,15 @@
         <f>COUNTIF(latest!$C$2:$C$2000,$A$11)</f>
         <v/>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="10">
         <f>IFERROR(_xlfn.MINIFS(latest!$H$2:$H$2000,latest!$C$2:$C$2000,$A$11),"-")</f>
         <v/>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="10">
         <f>IFERROR(AVERAGEIFS(latest!$H$2:$H$2000,latest!$C$2:$C$2000,$A$11),"-")</f>
         <v/>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="10">
         <f>IFERROR(_xlfn.MAXIFS(latest!$H$2:$H$2000,latest!$C$2:$C$2000,$A$11),"-")</f>
         <v/>
       </c>
@@ -7845,6 +8806,260 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="002E7D32"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Price evolution — cheapest R$ per carrier × category, by date</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>Control (R$/mo)</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="n"/>
+      <c r="D35" s="11" t="n"/>
+      <c r="E35" s="11" t="inlineStr">
+        <is>
+          <t>Post (R$/mo)</t>
+        </is>
+      </c>
+      <c r="F35" s="11" t="n"/>
+      <c r="G35" s="11" t="n"/>
+      <c r="H35" s="11" t="inlineStr">
+        <is>
+          <t>Pre (R$, recarga)</t>
+        </is>
+      </c>
+      <c r="I35" s="11" t="n"/>
+      <c r="J35" s="11" t="n"/>
+      <c r="K35" s="11" t="inlineStr">
+        <is>
+          <t>Digital (R$/mo)</t>
+        </is>
+      </c>
+      <c r="L35" s="11" t="n"/>
+      <c r="M35" s="11" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n"/>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>TIM</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>Vivo</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="inlineStr">
+        <is>
+          <t>Claro</t>
+        </is>
+      </c>
+      <c r="E36" s="11" t="inlineStr">
+        <is>
+          <t>TIM</t>
+        </is>
+      </c>
+      <c r="F36" s="11" t="inlineStr">
+        <is>
+          <t>Vivo</t>
+        </is>
+      </c>
+      <c r="G36" s="11" t="inlineStr">
+        <is>
+          <t>Claro</t>
+        </is>
+      </c>
+      <c r="H36" s="11" t="inlineStr">
+        <is>
+          <t>TIM</t>
+        </is>
+      </c>
+      <c r="I36" s="11" t="inlineStr">
+        <is>
+          <t>Vivo</t>
+        </is>
+      </c>
+      <c r="J36" s="11" t="inlineStr">
+        <is>
+          <t>Claro</t>
+        </is>
+      </c>
+      <c r="K36" s="11" t="inlineStr">
+        <is>
+          <t>TIM</t>
+        </is>
+      </c>
+      <c r="L36" s="11" t="inlineStr">
+        <is>
+          <t>Vivo</t>
+        </is>
+      </c>
+      <c r="M36" s="11" t="inlineStr">
+        <is>
+          <t>Claro</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B37" s="3">
+        <f>IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"control",history!$A:$A,$A37)=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"control",history!$A:$A,$A37))</f>
+        <v/>
+      </c>
+      <c r="C37" s="3">
+        <f>IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"control",history!$A:$A,$A37)=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"control",history!$A:$A,$A37))</f>
+        <v/>
+      </c>
+      <c r="D37" s="3">
+        <f>IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"control",history!$A:$A,$A37)=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"control",history!$A:$A,$A37))</f>
+        <v/>
+      </c>
+      <c r="E37" s="3">
+        <f>IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,$A37)=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"postpaid",history!$A:$A,$A37))</f>
+        <v/>
+      </c>
+      <c r="F37" s="3">
+        <f>IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,$A37)=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"postpaid",history!$A:$A,$A37))</f>
+        <v/>
+      </c>
+      <c r="G37" s="3">
+        <f>IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,$A37)=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"postpaid",history!$A:$A,$A37))</f>
+        <v/>
+      </c>
+      <c r="H37" s="3">
+        <f>IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"prepaid",history!$A:$A,$A37)=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"prepaid",history!$A:$A,$A37))</f>
+        <v/>
+      </c>
+      <c r="I37" s="3">
+        <f>IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"prepaid",history!$A:$A,$A37)=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"prepaid",history!$A:$A,$A37))</f>
+        <v/>
+      </c>
+      <c r="J37" s="3">
+        <f>IF(_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"prepaid",history!$A:$A,$A37)=0,"",_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"prepaid",history!$A:$A,$A37))</f>
+        <v/>
+      </c>
+      <c r="K37" s="3">
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"lite",history!$A:$A,$A37),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"tim",history!$D:$D,"flex",history!$A:$A,$A37),0)),"")</f>
+        <v/>
+      </c>
+      <c r="L37" s="3">
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"lite",history!$A:$A,$A37),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"vivo",history!$D:$D,"flex",history!$A:$A,$A37),0)),"")</f>
+        <v/>
+      </c>
+      <c r="M37" s="3">
+        <f>IFERROR(1/MAX(IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"lite",history!$A:$A,$A37),0),IFERROR(1/_xlfn.MINIFS(history!$H:$H,history!$C:$C,"claro",history!$D:$D,"flex",history!$A:$A,$A37),0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>Pre = cheapest recharge amount captured (true R$/day needs validity-days we don't yet capture — CONTEXT §8). Digital = min of Vivo Lite / Claro Flex. Daily rows now; monthly roll-up is the planned next step.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="E35:G35"/>
+    <mergeCell ref="K35:M35"/>
+    <mergeCell ref="H35:J35"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B37:D37">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E37:G37">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H37:J37">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K37:M37">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001565C0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -7861,51 +9076,51 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>Cross-operator comparison — within category, aligned by price rank</t>
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Ranking (today) — within category, aligned by price rank</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Pure Postpaid</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>Vivo R$</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>Claro R$</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>TIM R$</t>
         </is>
       </c>
-      <c r="E4" s="7" t="inlineStr">
+      <c r="E4" s="1" t="inlineStr">
         <is>
           <t>Vivo plan</t>
         </is>
       </c>
-      <c r="F4" s="7" t="inlineStr">
+      <c r="F4" s="1" t="inlineStr">
         <is>
           <t>Claro plan</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>TIM plan</t>
         </is>
@@ -7941,29 +9156,29 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" s="6" t="n">
         <v>165</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="C6" s="6" t="n">
         <v>164.9</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="6" t="n">
         <v>129.99</v>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Vivo Pós com Globoplay (60GB)</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>Pós 50GB com GeForce NOW (50GB)</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>TIM Black 70GB (70GB)</t>
         </is>
@@ -7999,29 +9214,29 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" s="6" t="n">
         <v>180</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="C8" s="6" t="n">
         <v>239.9</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" s="6" t="n">
         <v>149.99</v>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>Vivo Pós com Disney+ (60GB)</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>Pós 150GB (150GB)</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>TIM Black Plus 80GB (80GB)</t>
         </is>
@@ -8057,21 +9272,23 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B10" s="6" t="n">
         <v>180</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="C10" s="14" t="n"/>
+      <c r="D10" s="6" t="n">
         <v>159.99</v>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>Vivo Pós com Premiere (60GB)</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="F10" s="14" t="n"/>
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>TIM Black Premium 110GB (110GB)</t>
         </is>
@@ -8099,44 +9316,44 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>Control / Hybrid</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="1" t="inlineStr">
         <is>
           <t>Vivo R$</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>Claro R$</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D14" s="1" t="inlineStr">
         <is>
           <t>TIM R$</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E14" s="1" t="inlineStr">
         <is>
           <t>Vivo plan</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F14" s="1" t="inlineStr">
         <is>
           <t>Claro plan</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="G14" s="1" t="inlineStr">
         <is>
           <t>TIM plan</t>
         </is>
@@ -8172,29 +9389,29 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B16" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="C16" s="3" t="n">
+      <c r="B16" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="C16" s="6" t="n">
         <v>69.90000000000001</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="D16" s="6" t="n">
         <v>60.99</v>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Vivo Controle (51GB)</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Controle (61GB)</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>Controle 30GB (30GB)</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>TIM Controle Light Express 31GB (31GB)</t>
         </is>
@@ -8205,7 +9422,7 @@
         <v>3</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>99.90000000000001</v>
@@ -8215,7 +9432,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Vivo Controle Educação (51GB)</t>
+          <t>Vivo Controle Educação (61GB)</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8230,21 +9447,23 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B18" s="3" t="n">
-        <v>85</v>
-      </c>
-      <c r="D18" s="3" t="n">
+      <c r="B18" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="C18" s="14" t="n"/>
+      <c r="D18" s="6" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Vivo Controle Saúde (51GB)</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Controle Saúde (61GB)</t>
+        </is>
+      </c>
+      <c r="F18" s="14" t="n"/>
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>TIM Controle Pro Express</t>
         </is>
@@ -8255,14 +9474,14 @@
         <v>5</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>84.98999999999999</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Vivo Controle Música (51GB)</t>
+          <t>Vivo Controle Música (61GB)</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8272,77 +9491,81 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B20" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Vivo Controle Netflix (51GB)</t>
-        </is>
-      </c>
+      <c r="B20" s="6" t="n">
+        <v>95</v>
+      </c>
+      <c r="C20" s="14" t="n"/>
+      <c r="D20" s="14" t="n"/>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Vivo Controle Netflix (61GB)</t>
+        </is>
+      </c>
+      <c r="F20" s="14" t="n"/>
+      <c r="G20" s="14" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
         <v>7</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Vivo Controle Entretenimento (51GB)</t>
+          <t>Vivo Controle Entretenimento (61GB)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>Prepaid</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="A24" s="12" t="inlineStr">
         <is>
           <t>Note: prepaid is not a clean unit — Claro Prezão is a daily fee (R$1/dia) vs Vivo/TIM recharge amounts.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="A25" s="1" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B25" s="1" t="inlineStr">
         <is>
           <t>Vivo R$</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>Claro R$</t>
         </is>
       </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="D25" s="1" t="inlineStr">
         <is>
           <t>TIM R$</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
+      <c r="E25" s="1" t="inlineStr">
         <is>
           <t>Vivo plan</t>
         </is>
       </c>
-      <c r="F25" s="7" t="inlineStr">
+      <c r="F25" s="1" t="inlineStr">
         <is>
           <t>Claro plan</t>
         </is>
       </c>
-      <c r="G25" s="7" t="inlineStr">
+      <c r="G25" s="1" t="inlineStr">
         <is>
           <t>TIM plan</t>
         </is>
@@ -8378,21 +9601,23 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B27" s="3" t="n">
+      <c r="B27" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="C27" s="14" t="n"/>
+      <c r="D27" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>Vivo Pré (5GB)</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="F27" s="14" t="n"/>
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>TIM Pré XIP Plus 8GB (8GB)</t>
         </is>
@@ -8420,64 +9645,68 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B29" s="3" t="n">
+      <c r="B29" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="C29" s="14" t="n"/>
+      <c r="D29" s="14" t="n"/>
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>Vivo Pré (25GB)</t>
         </is>
       </c>
+      <c r="F29" s="14" t="n"/>
+      <c r="G29" s="14" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="A31" s="13" t="inlineStr">
         <is>
           <t>Digital</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="inlineStr">
+      <c r="A32" s="12" t="inlineStr">
         <is>
           <t>Digital = Vivo Lite + Claro Flex (TIM has no digital line).</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="7" t="inlineStr">
+      <c r="A33" s="1" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B33" s="1" t="inlineStr">
         <is>
           <t>Vivo R$</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>Claro R$</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D33" s="1" t="inlineStr">
         <is>
           <t>TIM R$</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr">
+      <c r="E33" s="1" t="inlineStr">
         <is>
           <t>Vivo plan</t>
         </is>
       </c>
-      <c r="F33" s="7" t="inlineStr">
+      <c r="F33" s="1" t="inlineStr">
         <is>
           <t>Claro plan</t>
         </is>
       </c>
-      <c r="G33" s="7" t="inlineStr">
+      <c r="G33" s="1" t="inlineStr">
         <is>
           <t>TIM plan</t>
         </is>
@@ -8505,25 +9734,27 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B35" s="3" t="n">
+      <c r="B35" s="6" t="n">
         <v>35</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="C35" s="6" t="n">
         <v>59.9</v>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="D35" s="14" t="n"/>
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>Easy Lite (20GB)</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>Flex 20GB (20GB)</t>
         </is>
       </c>
+      <c r="G35" s="14" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -8547,25 +9778,27 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B37" s="3" t="n">
+      <c r="B37" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="C37" s="6" t="n">
         <v>119.9</v>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="D37" s="14" t="n"/>
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>Easy Lite (30GB)</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>Flex 40GB (40GB)</t>
         </is>
       </c>
+      <c r="G37" s="14" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -8581,13 +9814,74 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B5:D11">
+    <cfRule type="expression" priority="1" dxfId="1" stopIfTrue="1">
+      <formula>AND(B5&lt;&gt;"",B5=MIN($B5:$D5))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B15:D21">
+    <cfRule type="expression" priority="3" dxfId="1" stopIfTrue="1">
+      <formula>AND(B15&lt;&gt;"",B15=MIN($B15:$D15))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B26:D29">
+    <cfRule type="expression" priority="5" dxfId="1" stopIfTrue="1">
+      <formula>AND(B26&lt;&gt;"",B26=MIN($B26:$D26))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B34:D38">
+    <cfRule type="expression" priority="7" dxfId="1" stopIfTrue="1">
+      <formula>AND(B34&lt;&gt;"",B34=MIN($B34:$D34))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00660099"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -8605,53 +9899,60 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Plan</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Price R$</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Promo R$</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Voice</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Unlimited apps</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Streaming</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>Postpaid</t>
         </is>
       </c>
+      <c r="B2" s="16" t="n"/>
+      <c r="C2" s="16" t="n"/>
+      <c r="D2" s="16" t="n"/>
+      <c r="E2" s="16" t="n"/>
+      <c r="F2" s="16" t="n"/>
+      <c r="G2" s="16" t="n"/>
+      <c r="H2" s="16" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -8678,28 +9979,28 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Vivo Pós com Globoplay</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="6" t="n">
         <v>165</v>
       </c>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>60 GB (50 GB de franquia 10 GB de bônus)</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Globoplay</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>Assinatura Globoplay inclusa</t>
         </is>
@@ -8734,28 +10035,28 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Vivo Pós com Disney+</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" s="6" t="n">
         <v>180</v>
       </c>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>60 GB (50 GB de franquia 10 GB de bônus)</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>Disney+</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>Assinatura Disney+ Padrão inclusa</t>
         </is>
@@ -8790,28 +10091,28 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Vivo Pós com Premiere</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" s="6" t="n">
         <v>180</v>
       </c>
-      <c r="C8" s="3" t="n"/>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>60 GB (50 GB de franquia 10 GB de bônus)</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="n"/>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>Premiere</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>Assinatura Premiere inclusa</t>
         </is>
@@ -8842,11 +10143,18 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>Control</t>
         </is>
       </c>
+      <c r="B10" s="16" t="n"/>
+      <c r="C10" s="16" t="n"/>
+      <c r="D10" s="16" t="n"/>
+      <c r="E10" s="16" t="n"/>
+      <c r="F10" s="16" t="n"/>
+      <c r="G10" s="16" t="n"/>
+      <c r="H10" s="16" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -8873,24 +10181,24 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>Vivo Controle</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>51 GB (20 GB de franquia 31 GB de bônus)</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="n"/>
-      <c r="F12" s="2" t="n"/>
-      <c r="G12" s="2" t="n"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="B12" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>61 GB (20 GB de franquia 31 GB de bônus)</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>6 meses grátis de Gemini com AI Plus</t>
         </is>
@@ -8903,12 +10211,12 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C13" s="3" t="n"/>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>51 GB (20 GB de franquia 31 GB de bônus)</t>
+          <t>61 GB (20 GB de franquia 31 GB de bônus)</t>
         </is>
       </c>
       <c r="E13" s="2" t="n"/>
@@ -8921,24 +10229,24 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>Vivo Controle Saúde</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n">
-        <v>85</v>
-      </c>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>51 GB (20 GB de franquia 31 GB de bônus)</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="n"/>
-      <c r="F14" s="2" t="n"/>
-      <c r="G14" s="2" t="n"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="B14" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>61 GB (20 GB de franquia 31 GB de bônus)</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>Assinatura Vale Saúde Sempre inclusa</t>
         </is>
@@ -8951,12 +10259,12 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="C15" s="3" t="n"/>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>51 GB (20 GB de franquia 31 GB de bônus)</t>
+          <t>61 GB (20 GB de franquia 31 GB de bônus)</t>
         </is>
       </c>
       <c r="E15" s="2" t="n"/>
@@ -8969,24 +10277,24 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>Vivo Controle Netflix</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="C16" s="3" t="n"/>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>51 GB (20 GB de franquia 31 GB de bônus)</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="n"/>
-      <c r="F16" s="2" t="n"/>
-      <c r="G16" s="2" t="n"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="B16" s="6" t="n">
+        <v>95</v>
+      </c>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>61 GB (20 GB de franquia 31 GB de bônus)</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>Assinatura Netflix Padrão com anúncios</t>
         </is>
@@ -8999,12 +10307,12 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C17" s="3" t="n"/>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>51 GB (20 GB de franquia 31 GB de bônus)</t>
+          <t>61 GB (20 GB de franquia 31 GB de bônus)</t>
         </is>
       </c>
       <c r="E17" s="2" t="n"/>
@@ -9017,11 +10325,18 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Digital</t>
         </is>
       </c>
+      <c r="B18" s="16" t="n"/>
+      <c r="C18" s="16" t="n"/>
+      <c r="D18" s="16" t="n"/>
+      <c r="E18" s="16" t="n"/>
+      <c r="F18" s="16" t="n"/>
+      <c r="G18" s="16" t="n"/>
+      <c r="H18" s="16" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -9044,24 +10359,24 @@
       <c r="H19" s="2" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>Easy Lite</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n">
+      <c r="B20" s="6" t="n">
         <v>35</v>
       </c>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>20 GB (20 GB de franquia 2 Meses de YouTube ilimitado)</t>
         </is>
       </c>
-      <c r="E20" s="2" t="n"/>
-      <c r="F20" s="2" t="n"/>
-      <c r="G20" s="2" t="n"/>
-      <c r="H20" s="2" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -9084,24 +10399,24 @@
       <c r="H21" s="2" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>Easy Lite</t>
         </is>
       </c>
-      <c r="B22" s="3" t="n">
+      <c r="B22" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="C22" s="3" t="n"/>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>30 GB</t>
         </is>
       </c>
-      <c r="E22" s="2" t="n"/>
-      <c r="F22" s="2" t="n"/>
-      <c r="G22" s="2" t="n"/>
-      <c r="H22" s="2" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -9124,11 +10439,18 @@
       <c r="H23" s="2" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+      <c r="A24" s="15" t="inlineStr">
         <is>
           <t>Prepaid</t>
         </is>
       </c>
+      <c r="B24" s="16" t="n"/>
+      <c r="C24" s="16" t="n"/>
+      <c r="D24" s="16" t="n"/>
+      <c r="E24" s="16" t="n"/>
+      <c r="F24" s="16" t="n"/>
+      <c r="G24" s="16" t="n"/>
+      <c r="H24" s="16" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -9151,24 +10473,24 @@
       <c r="H25" s="2" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>Vivo Pré</t>
         </is>
       </c>
-      <c r="B26" s="3" t="n">
+      <c r="B26" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="C26" s="3" t="n"/>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>5 GB (5 GB para navegar como quiser)</t>
         </is>
       </c>
-      <c r="E26" s="2" t="n"/>
-      <c r="F26" s="2" t="n"/>
-      <c r="G26" s="2" t="n"/>
-      <c r="H26" s="2" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -9191,33 +10513,82 @@
       <c r="H27" s="2" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>Vivo Pré</t>
         </is>
       </c>
-      <c r="B28" s="3" t="n">
+      <c r="B28" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="C28" s="3" t="n"/>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>25 GB (15 GB para navegar como quiser 5 GB de bônus 5 GB para navegar no Youtube)</t>
         </is>
       </c>
-      <c r="E28" s="2" t="n"/>
-      <c r="F28" s="2" t="n"/>
-      <c r="G28" s="2" t="n"/>
-      <c r="H28" s="2" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="5" t="n"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B3:B9">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B11:B17">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B19:B23">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B25:B28">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00DA291C"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -9235,53 +10606,60 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Plan</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Price R$</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Promo R$</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Voice</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Unlimited apps</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Streaming</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>Postpaid</t>
         </is>
       </c>
+      <c r="B2" s="16" t="n"/>
+      <c r="C2" s="16" t="n"/>
+      <c r="D2" s="16" t="n"/>
+      <c r="E2" s="16" t="n"/>
+      <c r="F2" s="16" t="n"/>
+      <c r="G2" s="16" t="n"/>
+      <c r="H2" s="16" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -9312,28 +10690,28 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Pós 50GB com GeForce NOW</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="6" t="n">
         <v>164.9</v>
       </c>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>50 GB</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>WhatsApp</t>
         </is>
       </c>
-      <c r="G4" s="2" t="n"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Américas; Claro Sync: Smartwatch conectado; Inclusa assinatura GeForce NOW</t>
         </is>
@@ -9368,28 +10746,28 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Pós 150GB</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" s="6" t="n">
         <v>239.9</v>
       </c>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>150 GB</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>WhatsApp</t>
         </is>
       </c>
-      <c r="G6" s="2" t="n"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>Armazenamento na nuvem:; Google One ou iCloud+; WhatsApp ilimitado; Roaming: Passaporte Américas e Europa; Claro Sync: Smartwatch conectado</t>
         </is>
@@ -9424,11 +10802,18 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>Control</t>
         </is>
       </c>
+      <c r="B8" s="16" t="n"/>
+      <c r="C8" s="16" t="n"/>
+      <c r="D8" s="16" t="n"/>
+      <c r="E8" s="16" t="n"/>
+      <c r="F8" s="16" t="n"/>
+      <c r="G8" s="16" t="n"/>
+      <c r="H8" s="16" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -9439,7 +10824,7 @@
       <c r="B9" s="3" t="n">
         <v>59.9</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="C9" s="17" t="n">
         <v>54.9</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -9461,28 +10846,28 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>Controle 30GB</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B10" s="6" t="n">
         <v>69.90000000000001</v>
       </c>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>30 GB</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n"/>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>WhatsApp</t>
         </is>
       </c>
-      <c r="G10" s="2" t="n"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>Para uso livre; Bônus do Hexa para uso livre; Bônus para redes sociais e apps; Redes sociais e apps; WhatsApp ilimitado</t>
         </is>
@@ -9517,11 +10902,18 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>Digital</t>
         </is>
       </c>
+      <c r="B12" s="16" t="n"/>
+      <c r="C12" s="16" t="n"/>
+      <c r="D12" s="16" t="n"/>
+      <c r="E12" s="16" t="n"/>
+      <c r="F12" s="16" t="n"/>
+      <c r="G12" s="16" t="n"/>
+      <c r="H12" s="16" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -9552,28 +10944,28 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>Flex 20GB</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n">
+      <c r="B14" s="6" t="n">
         <v>59.9</v>
       </c>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>20 GB</t>
         </is>
       </c>
-      <c r="E14" s="2" t="n"/>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>WhatsApp</t>
         </is>
       </c>
-      <c r="G14" s="2" t="n"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>Para uso livre; Bônus do Hexa para uso livre; Para redes sociais e apps; Bônus extra nos apps; WhatsApp ilimitado</t>
         </is>
@@ -9608,39 +11000,46 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>Flex 40GB</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n">
+      <c r="B16" s="6" t="n">
         <v>119.9</v>
       </c>
-      <c r="C16" s="3" t="n"/>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>40 GB</t>
         </is>
       </c>
-      <c r="E16" s="2" t="n"/>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>WhatsApp</t>
         </is>
       </c>
-      <c r="G16" s="2" t="n"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>Para uso livre; Para redes sociais e apps; Bônus uso livre; Bônus extra nos apps; WhatsApp ilimitado; Assinatura Claro musica inclusa</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>Prepaid</t>
         </is>
       </c>
+      <c r="B17" s="16" t="n"/>
+      <c r="C17" s="16" t="n"/>
+      <c r="D17" s="16" t="n"/>
+      <c r="E17" s="16" t="n"/>
+      <c r="F17" s="16" t="n"/>
+      <c r="G17" s="16" t="n"/>
+      <c r="H17" s="16" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -9667,13 +11066,62 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B3:B7">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B9:B11">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B13:B16">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B18">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="000033A0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -9691,53 +11139,60 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Plan</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Price R$</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Promo R$</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Voice</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Unlimited apps</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Streaming</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>Postpaid</t>
         </is>
       </c>
+      <c r="B2" s="16" t="n"/>
+      <c r="C2" s="16" t="n"/>
+      <c r="D2" s="16" t="n"/>
+      <c r="E2" s="16" t="n"/>
+      <c r="F2" s="16" t="n"/>
+      <c r="G2" s="16" t="n"/>
+      <c r="H2" s="16" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -9760,24 +11215,24 @@
       <c r="H3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>TIM Black 70GB</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="6" t="n">
         <v>129.99</v>
       </c>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>70 GB</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
-      <c r="G4" s="2" t="n"/>
-      <c r="H4" s="2" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -9800,24 +11255,24 @@
       <c r="H5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>TIM Black Plus 80GB</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" s="6" t="n">
         <v>149.99</v>
       </c>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>80 GB</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
-      <c r="G6" s="2" t="n"/>
-      <c r="H6" s="2" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -9840,24 +11295,24 @@
       <c r="H7" s="2" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>TIM Black Premium 110GB</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" s="6" t="n">
         <v>159.99</v>
       </c>
-      <c r="C8" s="3" t="n"/>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>110 GB</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="n"/>
-      <c r="G8" s="2" t="n"/>
-      <c r="H8" s="2" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -9880,11 +11335,18 @@
       <c r="H9" s="2" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>Control</t>
         </is>
       </c>
+      <c r="B10" s="16" t="n"/>
+      <c r="C10" s="16" t="n"/>
+      <c r="D10" s="16" t="n"/>
+      <c r="E10" s="16" t="n"/>
+      <c r="F10" s="16" t="n"/>
+      <c r="G10" s="16" t="n"/>
+      <c r="H10" s="16" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -9907,24 +11369,24 @@
       <c r="H11" s="2" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>TIM Controle Light Express 31GB</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B12" s="6" t="n">
         <v>60.99</v>
       </c>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>31 GB</t>
         </is>
       </c>
-      <c r="E12" s="2" t="n"/>
-      <c r="F12" s="2" t="n"/>
-      <c r="G12" s="2" t="n"/>
-      <c r="H12" s="2" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -9947,20 +11409,20 @@
       <c r="H13" s="2" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>TIM Controle Pro Express</t>
         </is>
       </c>
-      <c r="B14" s="3" t="n">
+      <c r="B14" s="6" t="n">
         <v>64.98999999999999</v>
       </c>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="2" t="n"/>
-      <c r="E14" s="2" t="n"/>
-      <c r="F14" s="2" t="n"/>
-      <c r="G14" s="2" t="n"/>
-      <c r="H14" s="2" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -9983,11 +11445,18 @@
       <c r="H15" s="2" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Prepaid</t>
         </is>
       </c>
+      <c r="B16" s="16" t="n"/>
+      <c r="C16" s="16" t="n"/>
+      <c r="D16" s="16" t="n"/>
+      <c r="E16" s="16" t="n"/>
+      <c r="F16" s="16" t="n"/>
+      <c r="G16" s="16" t="n"/>
+      <c r="H16" s="16" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -10010,24 +11479,24 @@
       <c r="H17" s="2" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>TIM Pré XIP Plus 8GB</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n">
+      <c r="B18" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="C18" s="3" t="n"/>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>8 GB</t>
         </is>
       </c>
-      <c r="E18" s="2" t="n"/>
-      <c r="F18" s="2" t="n"/>
-      <c r="G18" s="2" t="n"/>
-      <c r="H18" s="2" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -10050,6 +11519,42 @@
       <c r="H19" s="2" t="n"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B3:B9">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B11:B15">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B17:B19">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="0063BE7B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="00F8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/projects/mobile-price-tracker/backups/mobile_plans_2026-06-22.xlsx
+++ b/projects/mobile-price-tracker/backups/mobile_plans_2026-06-22.xlsx
@@ -1554,7 +1554,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -2528,7 +2528,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -2714,7 +2714,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -3464,7 +3464,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3744,7 +3744,7 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4848,7 +4848,7 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -5120,7 +5120,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -5616,7 +5616,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -6032,7 +6032,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -6094,7 +6094,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -6280,7 +6280,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -6340,7 +6340,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -6402,7 +6402,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -6650,7 +6650,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -6712,7 +6712,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -6774,7 +6774,7 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -6898,7 +6898,7 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -7030,7 +7030,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -7170,7 +7170,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -7240,7 +7240,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -7310,7 +7310,7 @@
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -7380,7 +7380,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -7450,7 +7450,7 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -7516,7 +7516,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -7582,7 +7582,7 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -7710,7 +7710,7 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -7916,7 +7916,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -7990,7 +7990,7 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -8138,7 +8138,7 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -8282,7 +8282,7 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -8348,7 +8348,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -8480,7 +8480,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22T18:35:49</t>
+          <t>2026-06-22T22:45:24</t>
         </is>
       </c>
     </row>
